--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2147"/>
+  <dimension ref="A1:K2207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.44" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="23.22" customWidth="1" style="114" min="1" max="1"/>
@@ -56750,1433 +56750,3053 @@
       <c r="K2094" s="40" t="n"/>
     </row>
     <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="A2095" s="0" t="inlineStr">
         <is>
           <t>संबंध</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2095" s="0" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="C2095" t="inlineStr">
+      <c r="C2095" s="0" t="inlineStr">
         <is>
           <t>sambandh</t>
         </is>
       </c>
-      <c r="F2095" t="inlineStr">
+      <c r="F2095" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Forms a key paired technical distinction with संपर्क (already in glossary as 'association/contact'); the corpus consistently pairs 'सम्पर्क एवं संबंध' as 'associations and relationships', with संबंध denoting the value-bound relational tie (esp. kinship/duty relations) as opposed to mere contact.</t>
         </is>
       </c>
-      <c r="I2095" t="inlineStr">
+      <c r="I2095" s="0" t="inlineStr">
         <is>
           <t>MVD p.243</t>
         </is>
       </c>
     </row>
     <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="A2096" s="0" t="inlineStr">
         <is>
           <t>युग</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2096" s="0" t="inlineStr">
         <is>
           <t>Age / Era</t>
         </is>
       </c>
-      <c r="C2096" t="inlineStr">
+      <c r="C2096" s="0" t="inlineStr">
         <is>
           <t>yug</t>
         </is>
       </c>
-      <c r="F2096" t="inlineStr">
+      <c r="F2096" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Names the stages in SB's historical periodization of human civilization, each rendered as a capitalized 'Age': जंगल युग=Jungle Age, शिला युग=Stone Age, धातु युग=Iron Age, दास युग=Submission Age, संघर्ष युग=Struggle Age.</t>
         </is>
       </c>
-      <c r="I2096" t="inlineStr">
+      <c r="I2096" s="0" t="inlineStr">
         <is>
           <t>SB p.23</t>
         </is>
       </c>
     </row>
     <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="A2097" s="0" t="inlineStr">
         <is>
           <t>उपलब्धि</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2097" s="0" t="inlineStr">
         <is>
           <t>Accomplishment / Attainment</t>
         </is>
       </c>
-      <c r="C2097" t="inlineStr">
+      <c r="C2097" s="0" t="inlineStr">
         <is>
           <t>upalabdhi</t>
         </is>
       </c>
-      <c r="F2097" t="inlineStr">
+      <c r="F2097" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Defined in the effort-accomplishment formula contrasted with श्रम (effortful strain): accomplishment exceeding hope is resolution, falling short of hope is shram; also used for accomplishment of resolution/humaneness.</t>
         </is>
       </c>
-      <c r="I2097" t="inlineStr">
+      <c r="I2097" s="0" t="inlineStr">
         <is>
           <t>MVD p.113</t>
         </is>
       </c>
     </row>
     <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="A2098" s="0" t="inlineStr">
         <is>
           <t>मूल्यांकन</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2098" s="0" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="C2098" t="inlineStr">
+      <c r="C2098" s="0" t="inlineStr">
         <is>
           <t>mulyankan</t>
         </is>
       </c>
-      <c r="F2098" t="inlineStr">
+      <c r="F2098" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Core term in the value/relationship framework, defined equivalent to भाव (sentiment) and made the basis for right-use of every relationship ('every aspect of human beings' needs मूल्यांकन'); consistently rendered as 'evaluation'.</t>
         </is>
       </c>
-      <c r="I2098" t="inlineStr">
+      <c r="I2098" s="0" t="inlineStr">
         <is>
           <t>MVD p.236</t>
         </is>
       </c>
     </row>
     <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="A2099" s="0" t="inlineStr">
         <is>
           <t>केन्द्रित</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2099" s="0" t="inlineStr">
         <is>
           <t>-centric / Centered</t>
         </is>
       </c>
-      <c r="C2099" t="inlineStr">
+      <c r="C2099" s="0" t="inlineStr">
         <is>
           <t>kendrit</t>
         </is>
       </c>
-      <c r="F2099" t="inlineStr">
+      <c r="F2099" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Used to classify philosophical traditions by their basis: मानव केंद्रित चिंतन (human-centric contemplation, i.e. Madhyasth Darshan itself) vs ईश्वर केंद्रित (God-centric/idealism) vs वस्तु केंद्रित (object-centric/materialism); rendered consistently as '-centric'.</t>
         </is>
       </c>
-      <c r="I2099" t="inlineStr">
+      <c r="I2099" s="0" t="inlineStr">
         <is>
           <t>MVD p.3</t>
         </is>
       </c>
     </row>
     <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="A2100" s="0" t="inlineStr">
         <is>
           <t>इतिहास</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2100" s="0" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="C2100" t="inlineStr">
+      <c r="C2100" s="0" t="inlineStr">
         <is>
           <t>itihaas</t>
         </is>
       </c>
-      <c r="F2100" t="inlineStr">
+      <c r="F2100" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Given an explicit technical definition in the text: the language/word-collection used to recall the chronological record of past actions and events toward humaneness; rendered consistently as 'history'.</t>
         </is>
       </c>
-      <c r="I2100" t="inlineStr">
+      <c r="I2100" s="0" t="inlineStr">
         <is>
           <t>MVD p.135</t>
         </is>
       </c>
     </row>
     <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="A2101" s="0" t="inlineStr">
         <is>
           <t>सर्वतोमुखी</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2101" s="0" t="inlineStr">
         <is>
           <t>Comprehensive</t>
         </is>
       </c>
-      <c r="C2101" t="inlineStr">
+      <c r="C2101" s="0" t="inlineStr">
         <is>
           <t>sarvatomukhi</t>
         </is>
       </c>
-      <c r="F2101" t="inlineStr">
+      <c r="F2101" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Recurring technical adjective modifying समाधान and used alongside अभ्युदय, consistently rendered "comprehensive" in the fixed phrase "comprehensive resolution".</t>
         </is>
       </c>
-      <c r="I2101" t="inlineStr">
+      <c r="I2101" s="0" t="inlineStr">
         <is>
           <t>MVD p.23</t>
         </is>
       </c>
     </row>
     <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="A2102" s="0" t="inlineStr">
         <is>
           <t>अज्ञान</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2102" s="0" t="inlineStr">
         <is>
           <t>Ignorance</t>
         </is>
       </c>
-      <c r="C2102" t="inlineStr">
+      <c r="C2102" s="0" t="inlineStr">
         <is>
           <t>agyan</t>
         </is>
       </c>
-      <c r="F2102" t="inlineStr">
+      <c r="F2102" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Explicitly defined synonym-pair with अविद्या ("अविद्या अथवा अज्ञान") meaning lack of awakening to understand a thing's true form/properties/nature/dharma; distinct from अज्ञानी (the ignorant person) which is already glossed.</t>
         </is>
       </c>
-      <c r="I2102" t="inlineStr">
+      <c r="I2102" s="0" t="inlineStr">
         <is>
           <t>MVD p.184</t>
         </is>
       </c>
     </row>
     <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="A2103" s="0" t="inlineStr">
         <is>
           <t>हृदय</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2103" s="0" t="inlineStr">
         <is>
           <t>Heart</t>
         </is>
       </c>
-      <c r="C2103" t="inlineStr">
+      <c r="C2103" s="0" t="inlineStr">
         <is>
           <t>hriday</t>
         </is>
       </c>
-      <c r="F2103" t="inlineStr">
+      <c r="F2103" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Technical link in the mun-prana-hriday-sharir chain (mind - vital force - heart - body) describing sensory/instinctual activity; translator renders it "heart" but has inconsistently glossed it as "(senses)" vs "(the body)" across occurrences, suggesting a fixed rendering is needed.</t>
         </is>
       </c>
-      <c r="I2103" t="inlineStr">
+      <c r="I2103" s="0" t="inlineStr">
         <is>
           <t>MVD p.208</t>
         </is>
       </c>
     </row>
     <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="A2104" s="0" t="inlineStr">
         <is>
           <t>सहअस्तित्ववाद</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2104" s="0" t="inlineStr">
         <is>
           <t>Coexistentialism</t>
         </is>
       </c>
-      <c r="C2104" t="inlineStr">
+      <c r="C2104" s="0" t="inlineStr">
         <is>
           <t>Sah-astitvavad</t>
         </is>
       </c>
-      <c r="F2104" t="inlineStr">
+      <c r="F2104" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Name of the overall philosophical system/ism ("Madhyasth Darshan Sahastitvavad"), distinct from सहअस्तित्व (coexistence, the state) which is already glossed separately.</t>
         </is>
       </c>
-      <c r="I2104" t="inlineStr">
+      <c r="I2104" s="0" t="inlineStr">
         <is>
           <t>MVD p.3</t>
         </is>
       </c>
     </row>
     <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="A2105" s="0" t="inlineStr">
         <is>
           <t>अंश</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2105" s="0" t="inlineStr">
         <is>
           <t>Particle</t>
         </is>
       </c>
-      <c r="C2105" t="inlineStr">
+      <c r="C2105" s="0" t="inlineStr">
         <is>
           <t>ansh</t>
         </is>
       </c>
-      <c r="F2105" t="inlineStr">
+      <c r="F2105" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Core atomic-theory term for the sub-units composing a परमाणु (atom), as in "परमाणु अंश" (atomic particle) and मध्यांश (nucleus, lit. middle-particle); consistently rendered "particle".</t>
         </is>
       </c>
-      <c r="I2105" t="inlineStr">
+      <c r="I2105" s="0" t="inlineStr">
         <is>
           <t>MVD p.78</t>
         </is>
       </c>
     </row>
     <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="A2106" s="0" t="inlineStr">
         <is>
           <t>साकार</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2106" s="0" t="inlineStr">
         <is>
           <t>Manifested (having form)</t>
         </is>
       </c>
-      <c r="C2106" t="inlineStr">
+      <c r="C2106" s="0" t="inlineStr">
         <is>
           <t>sakar</t>
         </is>
       </c>
-      <c r="F2106" t="inlineStr">
+      <c r="F2106" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Natural paired opposite of निराकार (already glossed as "formless"); denotes taking concrete form/materialising, e.g. "मनाकार साकार होना" = "materialisation of ideas".</t>
         </is>
       </c>
-      <c r="I2106" t="inlineStr">
+      <c r="I2106" s="0" t="inlineStr">
         <is>
           <t>MVD p.209</t>
         </is>
       </c>
     </row>
     <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="A2107" s="0" t="inlineStr">
         <is>
           <t>स्वभावगति</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2107" s="0" t="inlineStr">
         <is>
           <t>natural state</t>
         </is>
       </c>
-      <c r="C2107" t="inlineStr">
+      <c r="C2107" s="0" t="inlineStr">
         <is>
           <t>svabhav-gati</t>
         </is>
       </c>
-      <c r="F2107" t="inlineStr">
+      <c r="F2107" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Denotes a unit's or nature's own inherent/natural condition of movement, contrasted with आवेशित गति (excited state); e.g. Earth's or vegetation's 'natural state' (SB p.16, p.52).</t>
         </is>
       </c>
-      <c r="I2107" t="inlineStr">
+      <c r="I2107" s="0" t="inlineStr">
         <is>
           <t>SB p.16</t>
         </is>
       </c>
     </row>
     <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="A2108" s="0" t="inlineStr">
         <is>
           <t>परम्परा</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2108" s="0" t="inlineStr">
         <is>
           <t>tradition</t>
         </is>
       </c>
-      <c r="C2108" t="inlineStr">
+      <c r="C2108" s="0" t="inlineStr">
         <is>
           <t>parampara</t>
         </is>
       </c>
-      <c r="F2108" t="inlineStr">
+      <c r="F2108" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Recurring key term for social/human continuity of practice, e.g. 'जागृत मानव परम्परा' rendered 'the awakened human tradition' (MVD p.300).</t>
         </is>
       </c>
-      <c r="I2108" t="inlineStr">
+      <c r="I2108" s="0" t="inlineStr">
         <is>
           <t>MVD p.300</t>
         </is>
       </c>
     </row>
     <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="A2109" s="0" t="inlineStr">
         <is>
           <t>सिद्धान्त</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2109" s="0" t="inlineStr">
         <is>
           <t>principle</t>
         </is>
       </c>
-      <c r="C2109" t="inlineStr">
+      <c r="C2109" s="0" t="inlineStr">
         <is>
           <t>siddhant</t>
         </is>
       </c>
-      <c r="F2109" t="inlineStr">
+      <c r="F2109" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Used for foundational principles, e.g. 'श्रम-गति-परिणाम' is titled 'The Principle', and 'सहअस्तित्व सिद्धान्त' = 'principle of coexistence' (MVD p.11, p.265).</t>
         </is>
       </c>
-      <c r="I2109" t="inlineStr">
+      <c r="I2109" s="0" t="inlineStr">
         <is>
           <t>MVD p.11</t>
         </is>
       </c>
     </row>
     <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="A2110" s="0" t="inlineStr">
         <is>
           <t>धर्मनीति</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2110" s="0" t="inlineStr">
         <is>
           <t>Moral policy</t>
         </is>
       </c>
-      <c r="C2110" t="inlineStr">
+      <c r="C2110" s="0" t="inlineStr">
         <is>
           <t>dharmaniti</t>
         </is>
       </c>
-      <c r="F2110" t="inlineStr">
+      <c r="F2110" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Paired technical term with राज्यनीति (State policy); defined as the policy for right-use of wealth (tan-man-dhan) (MVD p.242).</t>
         </is>
       </c>
-      <c r="I2110" t="inlineStr">
+      <c r="I2110" s="0" t="inlineStr">
         <is>
           <t>MVD p.242</t>
         </is>
       </c>
     </row>
     <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="A2111" s="0" t="inlineStr">
         <is>
           <t>वनस्पति</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2111" s="0" t="inlineStr">
         <is>
           <t>vegetation / plant</t>
         </is>
       </c>
-      <c r="C2111" t="inlineStr">
+      <c r="C2111" s="0" t="inlineStr">
         <is>
           <t>vanaspati</t>
         </is>
       </c>
-      <c r="F2111" t="inlineStr">
+      <c r="F2111" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Base classification noun for the biological/plant order (प्राणावस्था), consistently rendered 'vegetation' or 'plant forms' (MVD p.47, p.203).</t>
         </is>
       </c>
-      <c r="I2111" t="inlineStr">
+      <c r="I2111" s="0" t="inlineStr">
         <is>
           <t>MVD p.47</t>
         </is>
       </c>
     </row>
     <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="A2112" s="0" t="inlineStr">
         <is>
           <t>गठनपूर्णता</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2112" s="0" t="inlineStr">
         <is>
           <t>constitutional completeness</t>
         </is>
       </c>
-      <c r="C2112" t="inlineStr">
+      <c r="C2112" s="0" t="inlineStr">
         <is>
           <t>gathan-purnata</t>
         </is>
       </c>
-      <c r="F2112" t="inlineStr">
+      <c r="F2112" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Technical term for the stage at which an atom completes its constitution/structure and becomes a jeevan-atom (MVD p.91, SB p.51).</t>
         </is>
       </c>
-      <c r="I2112" t="inlineStr">
+      <c r="I2112" s="0" t="inlineStr">
         <is>
           <t>MVD p.91</t>
         </is>
       </c>
     </row>
     <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="A2113" s="0" t="inlineStr">
         <is>
           <t>हिताहित</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2113" s="0" t="inlineStr">
         <is>
           <t>healthy-unhealthy</t>
         </is>
       </c>
-      <c r="C2113" t="inlineStr">
+      <c r="C2113" s="0" t="inlineStr">
         <is>
           <t>hitahit</t>
         </is>
       </c>
-      <c r="F2113" t="inlineStr">
+      <c r="F2113" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the fixed six perspectives (प्रियाप्रिय, हिताहित, लाभालाभ, न्यायान्याय, धर्माधर्म, सत्यासत्य) through which behaviour is analysed; consistently rendered 'healthy-unhealthy' (MVD p.67).</t>
         </is>
       </c>
-      <c r="I2113" t="inlineStr">
+      <c r="I2113" s="0" t="inlineStr">
         <is>
           <t>MVD p.67</t>
         </is>
       </c>
     </row>
     <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="A2114" s="0" t="inlineStr">
         <is>
           <t>शांति</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2114" s="0" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="C2114" t="inlineStr">
+      <c r="C2114" s="0" t="inlineStr">
         <is>
           <t>shanti</t>
         </is>
       </c>
-      <c r="F2114" t="inlineStr">
+      <c r="F2114" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Explicitly defined technical term: the effect of truth-realised atma upon vritti; part of the defined quartet सुख-शांति-संतोष-आनंद (MVD p.101, p.180).</t>
         </is>
       </c>
-      <c r="I2114" t="inlineStr">
+      <c r="I2114" s="0" t="inlineStr">
         <is>
           <t>MVD p.101</t>
         </is>
       </c>
     </row>
     <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="A2115" s="0" t="inlineStr">
         <is>
           <t>पोषक</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2115" s="0" t="inlineStr">
         <is>
           <t>nurturing</t>
         </is>
       </c>
-      <c r="C2115" t="inlineStr">
+      <c r="C2115" s="0" t="inlineStr">
         <is>
           <t>poshak</t>
         </is>
       </c>
-      <c r="F2115" t="inlineStr">
+      <c r="F2115" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Core dichotomy term paired with शोषक ('exploitative'); describes behaviour/relationships that nurture rather than exploit (MVD p.161, p.241).</t>
         </is>
       </c>
-      <c r="I2115" t="inlineStr">
+      <c r="I2115" s="0" t="inlineStr">
         <is>
           <t>MVD p.241</t>
         </is>
       </c>
     </row>
     <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="A2116" s="0" t="inlineStr">
         <is>
           <t>दास युग</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2116" s="0" t="inlineStr">
         <is>
           <t>Submission Age</t>
         </is>
       </c>
-      <c r="C2116" t="inlineStr">
+      <c r="C2116" s="0" t="inlineStr">
         <is>
           <t>das yug</t>
         </is>
       </c>
-      <c r="F2116" t="inlineStr">
+      <c r="F2116" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Named historical epoch in the periodization जंगल→शिला→धातु→दास→संघर्ष युग, consistently rendered 'Submission Age' (SB p.23).</t>
         </is>
       </c>
-      <c r="I2116" t="inlineStr">
+      <c r="I2116" s="0" t="inlineStr">
         <is>
           <t>SB p.23</t>
         </is>
       </c>
     </row>
     <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="A2117" s="0" t="inlineStr">
         <is>
           <t>विधायिका</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2117" s="0" t="inlineStr">
         <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="C2117" t="inlineStr">
+      <c r="C2117" s="0" t="inlineStr">
         <is>
           <t>vidhayika</t>
         </is>
       </c>
-      <c r="F2117" t="inlineStr">
+      <c r="F2117" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Institutional term used in SB's discussion of government departments (कार्यपालिका/विधायिका/न्यायपालिका), consistently rendered 'legislature/legislative' (SB p.31).</t>
         </is>
       </c>
-      <c r="I2117" t="inlineStr">
+      <c r="I2117" s="0" t="inlineStr">
         <is>
           <t>SB p.31</t>
         </is>
       </c>
     </row>
     <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="A2118" s="0" t="inlineStr">
         <is>
           <t>सेवा</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2118" s="0" t="inlineStr">
         <is>
           <t>service (seva)</t>
         </is>
       </c>
-      <c r="C2118" t="inlineStr">
+      <c r="C2118" s="0" t="inlineStr">
         <is>
           <t>seva</t>
         </is>
       </c>
-      <c r="F2118" t="inlineStr">
+      <c r="F2118" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Explicitly defined technical term: the tendency to derive satisfaction from benevolent acts, distinguished from remuneration-based service (MVD p.73).</t>
         </is>
       </c>
-      <c r="I2118" t="inlineStr">
+      <c r="I2118" s="0" t="inlineStr">
         <is>
           <t>MVD p.73</t>
         </is>
       </c>
     </row>
     <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="A2119" s="0" t="inlineStr">
         <is>
           <t>आनन्द</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2119" s="0" t="inlineStr">
         <is>
           <t>bliss</t>
         </is>
       </c>
-      <c r="C2119" t="inlineStr">
+      <c r="C2119" s="0" t="inlineStr">
         <is>
           <t>aanand</t>
         </is>
       </c>
-      <c r="F2119" t="inlineStr">
+      <c r="F2119" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Fourth term in the defined quartet सुख-शांति-संतोष-आनंद (happiness-peace-contentment-bliss) describing the dharma of humans (MVD p.16, p.180).</t>
         </is>
       </c>
-      <c r="I2119" t="inlineStr">
+      <c r="I2119" s="0" t="inlineStr">
         <is>
           <t>MVD p.16</t>
         </is>
       </c>
     </row>
     <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="A2120" s="0" t="inlineStr">
         <is>
           <t>सत्यानुभूति</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2120" s="0" t="inlineStr">
         <is>
           <t>realisation in truth</t>
         </is>
       </c>
-      <c r="C2120" t="inlineStr">
+      <c r="C2120" s="0" t="inlineStr">
         <is>
           <t>satya-anubhuti</t>
         </is>
       </c>
-      <c r="F2120" t="inlineStr">
+      <c r="F2120" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Core defined term equating awakening (जागृति) with truth-realisation/liberation from delusion, central to the model of जागृति (MVD p.18, p.160).</t>
         </is>
       </c>
-      <c r="I2120" t="inlineStr">
+      <c r="I2120" s="0" t="inlineStr">
         <is>
           <t>MVD p.18</t>
         </is>
       </c>
     </row>
     <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="A2121" s="0" t="inlineStr">
         <is>
           <t>द्वन्द्व</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2121" s="0" t="inlineStr">
         <is>
           <t>Duality</t>
         </is>
       </c>
-      <c r="C2121" t="inlineStr">
+      <c r="C2121" s="0" t="inlineStr">
         <is>
           <t>dwandwa</t>
         </is>
       </c>
-      <c r="F2121" t="inlineStr">
+      <c r="F2121" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Named as the direct counterpart/antithesis of समाधान (Resolution) in a section title, 'समाधान और द्वन्द्व' rendered 'Resolution and Duality' (SB p.13); also rendered 'conflict' in adversarial contexts (MVD p.184). Root of the existing compound entry अंर्तद्वंद्व = Internal conflict, but the base term itself is not yet in the glossary.</t>
         </is>
       </c>
-      <c r="I2121" t="inlineStr">
+      <c r="I2121" s="0" t="inlineStr">
         <is>
           <t>SB p.13</t>
         </is>
       </c>
     </row>
     <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="A2122" s="0" t="inlineStr">
         <is>
           <t>सानुकूलता</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2122" s="0" t="inlineStr">
         <is>
           <t>Conduciveness</t>
         </is>
       </c>
-      <c r="C2122" t="inlineStr">
+      <c r="C2122" s="0" t="inlineStr">
         <is>
           <t>sanukulta</t>
         </is>
       </c>
-      <c r="F2122" t="inlineStr">
+      <c r="F2122" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Recurring technical term in SB for the harmonious/congruent relation between a unit and its environment, paired antonymically with प्रतिकूलता (adverseness); consistently rendered 'conduciveness'/'conducive conditions' (SB p.15: 'elements of conducive conditions'; SB p.17: 'conduciveness ... of the animal order').</t>
         </is>
       </c>
-      <c r="I2122" t="inlineStr">
+      <c r="I2122" s="0" t="inlineStr">
         <is>
           <t>SB p.15</t>
         </is>
       </c>
     </row>
     <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="A2123" s="0" t="inlineStr">
         <is>
           <t>प्रियाप्रिय</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2123" s="0" t="inlineStr">
         <is>
           <t>pleasant-unpleasant</t>
         </is>
       </c>
-      <c r="C2123" t="inlineStr">
+      <c r="C2123" s="0" t="inlineStr">
         <is>
           <t>Priyapriya</t>
         </is>
       </c>
-      <c r="F2123" t="inlineStr">
+      <c r="F2123" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the six paired 'drishti' (perspectives) formally enumerated together with hitahit, labhalabh, nyayanyaya, dharmadharma, satyasatya as the six dimensions of behavioural evaluation.</t>
         </is>
       </c>
-      <c r="I2123" t="inlineStr">
+      <c r="I2123" s="0" t="inlineStr">
         <is>
           <t>MVD p.67</t>
         </is>
       </c>
     </row>
     <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="A2124" s="0" t="inlineStr">
         <is>
           <t>न्यायान्याय</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2124" s="0" t="inlineStr">
         <is>
           <t>justice-injustice</t>
         </is>
       </c>
-      <c r="C2124" t="inlineStr">
+      <c r="C2124" s="0" t="inlineStr">
         <is>
           <t>Nyayanyaya</t>
         </is>
       </c>
-      <c r="F2124" t="inlineStr">
+      <c r="F2124" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the six paired 'drishti' (perspectives) of behaviour, listed alongside priyapriya, hitahit, labhalabh, dharmadharma, satyasatya.</t>
         </is>
       </c>
-      <c r="I2124" t="inlineStr">
+      <c r="I2124" s="0" t="inlineStr">
         <is>
           <t>MVD p.67</t>
         </is>
       </c>
     </row>
     <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="A2125" s="0" t="inlineStr">
         <is>
           <t>धर्माधर्म</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2125" s="0" t="inlineStr">
         <is>
           <t>dharma-adharma</t>
         </is>
       </c>
-      <c r="C2125" t="inlineStr">
+      <c r="C2125" s="0" t="inlineStr">
         <is>
           <t>Dharmadharma</t>
         </is>
       </c>
-      <c r="F2125" t="inlineStr">
+      <c r="F2125" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the six paired 'drishti' (perspectives) of behaviour in the same enumerated set as nyayanyaya and satyasatya.</t>
         </is>
       </c>
-      <c r="I2125" t="inlineStr">
+      <c r="I2125" s="0" t="inlineStr">
         <is>
           <t>MVD p.67</t>
         </is>
       </c>
     </row>
     <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="A2126" s="0" t="inlineStr">
         <is>
           <t>सत्यासत्य</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2126" s="0" t="inlineStr">
         <is>
           <t>truth-untruth</t>
         </is>
       </c>
-      <c r="C2126" t="inlineStr">
+      <c r="C2126" s="0" t="inlineStr">
         <is>
           <t>Satyasatya</t>
         </is>
       </c>
-      <c r="F2126" t="inlineStr">
+      <c r="F2126" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the six paired 'drishti' (perspectives) of behaviour in the same enumerated set as nyayanyaya and dharmadharma.</t>
         </is>
       </c>
-      <c r="I2126" t="inlineStr">
+      <c r="I2126" s="0" t="inlineStr">
         <is>
           <t>MVD p.67</t>
         </is>
       </c>
     </row>
     <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="A2127" s="0" t="inlineStr">
         <is>
           <t>राज्यनीति</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2127" s="0" t="inlineStr">
         <is>
           <t>State policy</t>
         </is>
       </c>
-      <c r="C2127" t="inlineStr">
+      <c r="C2127" s="0" t="inlineStr">
         <is>
           <t>Rajyaniti</t>
         </is>
       </c>
-      <c r="F2127" t="inlineStr">
+      <c r="F2127" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Paired counterpart to Moral policy (धर्मनीति) in the system's political taxonomy; consistently capitalized/rendered as 'State policy' concerned with security of resources.</t>
         </is>
       </c>
-      <c r="I2127" t="inlineStr">
+      <c r="I2127" s="0" t="inlineStr">
         <is>
           <t>MVD p.234</t>
         </is>
       </c>
     </row>
     <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="A2128" s="0" t="inlineStr">
         <is>
           <t>मित्र</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2128" s="0" t="inlineStr">
         <is>
           <t>Friend</t>
         </is>
       </c>
-      <c r="C2128" t="inlineStr">
+      <c r="C2128" s="0" t="inlineStr">
         <is>
           <t>Mitra</t>
         </is>
       </c>
-      <c r="F2128" t="inlineStr">
+      <c r="F2128" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Formally defined relationship term in the system's relationship taxonomy (alongside guru-shishya, saathi-sahyogi): 'one in whom there is absence of animosity'.</t>
         </is>
       </c>
-      <c r="I2128" t="inlineStr">
+      <c r="I2128" s="0" t="inlineStr">
         <is>
           <t>MVD p.253</t>
         </is>
       </c>
     </row>
     <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="A2129" s="0" t="inlineStr">
         <is>
           <t>आश्रय</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2129" s="0" t="inlineStr">
         <is>
           <t>refuge</t>
         </is>
       </c>
-      <c r="C2129" t="inlineStr">
+      <c r="C2129" s="0" t="inlineStr">
         <is>
           <t>Aashray</t>
         </is>
       </c>
-      <c r="F2129" t="inlineStr">
+      <c r="F2129" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Technical relational term for hierarchical dependency/containment (e.g. mun in the refuge of vritti, vritti in the refuge of chitta; being in the refuge of the ideal), consistently rendered 'refuge'.</t>
         </is>
       </c>
-      <c r="I2129" t="inlineStr">
+      <c r="I2129" s="0" t="inlineStr">
         <is>
           <t>MVD p.279</t>
         </is>
       </c>
     </row>
     <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="A2130" s="0" t="inlineStr">
         <is>
           <t>वाङ्मय</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2130" s="0" t="inlineStr">
         <is>
           <t>body of thought / literature</t>
         </is>
       </c>
-      <c r="C2130" t="inlineStr">
+      <c r="C2130" s="0" t="inlineStr">
         <is>
           <t>Vaangmaya</t>
         </is>
       </c>
-      <c r="F2130" t="inlineStr">
+      <c r="F2130" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Refers to an entire corpus of ideology/literature produced around a school of thought (e.g. 'materialist vaangmaya'), rendered as 'body of thought' or 'literature' depending on context.</t>
         </is>
       </c>
-      <c r="I2130" t="inlineStr">
+      <c r="I2130" s="0" t="inlineStr">
         <is>
           <t>SB p.25</t>
         </is>
       </c>
     </row>
     <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="A2131" s="0" t="inlineStr">
         <is>
           <t>विकासक्रम</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2131" s="0" t="inlineStr">
         <is>
           <t>development progression</t>
         </is>
       </c>
-      <c r="C2131" t="inlineStr">
+      <c r="C2131" s="0" t="inlineStr">
         <is>
           <t>Vikaskram</t>
         </is>
       </c>
-      <c r="F2131" t="inlineStr">
+      <c r="F2131" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Distinct compound from विकास (development) alone; the text itself glosses it with the transliteration 'vikas kram', denoting the ongoing progression/sequence of development in nature.</t>
         </is>
       </c>
-      <c r="I2131" t="inlineStr">
+      <c r="I2131" s="0" t="inlineStr">
         <is>
           <t>MVD p.7</t>
         </is>
       </c>
     </row>
     <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="A2132" s="0" t="inlineStr">
         <is>
           <t>लाभालाभ</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2132" s="0" t="inlineStr">
         <is>
           <t>profit-loss</t>
         </is>
       </c>
-      <c r="C2132" t="inlineStr">
+      <c r="C2132" s="0" t="inlineStr">
         <is>
           <t>labhalabh</t>
         </is>
       </c>
-      <c r="F2132" t="inlineStr">
+      <c r="F2132" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the six paired dvandva perspectives (प्रियाप्रिय, हिताहित, लाभालाभ, न्यायान्याय, धर्माधर्म, सत्यासत्य) through which all human behaviour is manifest; rendered profit-loss when listing the inhumane/amanveeya perspectives.</t>
         </is>
       </c>
-      <c r="I2132" t="inlineStr">
+      <c r="I2132" s="0" t="inlineStr">
         <is>
           <t>MVD p.58</t>
         </is>
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="A2133" s="0" t="inlineStr">
         <is>
           <t>अध्यापक</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2133" s="0" t="inlineStr">
         <is>
           <t>Teacher (adhyapak)</t>
         </is>
       </c>
-      <c r="C2133" t="inlineStr">
+      <c r="C2133" s="0" t="inlineStr">
         <is>
           <t>adhyapak</t>
         </is>
       </c>
-      <c r="F2133" t="inlineStr">
+      <c r="F2133" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Formally defined technical role: one who imparts realisation of truth-as-coexistence through the realisation-based/experiential method, distinct from an ordinary school teacher.</t>
         </is>
       </c>
-      <c r="I2133" t="inlineStr">
+      <c r="I2133" s="0" t="inlineStr">
         <is>
           <t>MVD p.150</t>
         </is>
       </c>
     </row>
     <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="A2134" s="0" t="inlineStr">
         <is>
           <t>फलन</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2134" s="0" t="inlineStr">
         <is>
           <t>function/outcome</t>
         </is>
       </c>
-      <c r="C2134" t="inlineStr">
+      <c r="C2134" s="0" t="inlineStr">
         <is>
           <t>phalan</t>
         </is>
       </c>
-      <c r="F2134" t="inlineStr">
+      <c r="F2134" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Denotes a functional (mathematical-style) interdependence between two factors yielding a third, e.g. गति एवं परिणाम के फलन में उपलब्धि श्रम है rendered as 'the outcome of motion and result is effort'; translator often folds it into paraphrase rather than a fixed word.</t>
         </is>
       </c>
-      <c r="I2134" t="inlineStr">
+      <c r="I2134" s="0" t="inlineStr">
         <is>
           <t>MVD p.105</t>
         </is>
       </c>
     </row>
     <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="A2135" s="0" t="inlineStr">
         <is>
           <t>भौतिकता</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2135" s="0" t="inlineStr">
         <is>
           <t>materiality</t>
         </is>
       </c>
-      <c r="C2135" t="inlineStr">
+      <c r="C2135" s="0" t="inlineStr">
         <is>
           <t>bhautikta</t>
         </is>
       </c>
-      <c r="F2135" t="inlineStr">
+      <c r="F2135" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Distinct from भौतिकवाद (materialism, the ideology) - denotes the physical/material quality itself, e.g. prosperity in the physical aspect, and materiality propounded as dialectical.</t>
         </is>
       </c>
-      <c r="I2135" t="inlineStr">
+      <c r="I2135" s="0" t="inlineStr">
         <is>
           <t>MVD p.96</t>
         </is>
       </c>
     </row>
     <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="A2136" s="0" t="inlineStr">
         <is>
           <t>सत्यानुभूत</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2136" s="0" t="inlineStr">
         <is>
           <t>truth-realised</t>
         </is>
       </c>
-      <c r="C2136" t="inlineStr">
+      <c r="C2136" s="0" t="inlineStr">
         <is>
           <t>satyanubhoot</t>
         </is>
       </c>
-      <c r="F2136" t="inlineStr">
+      <c r="F2136" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Standard qualifier for आत्मा (atma) used to define आनंद/सुख/शांति/चिदानंद as the effect of truth-realised atma on buddhi/mun/vritti/chitta respectively.</t>
         </is>
       </c>
-      <c r="I2136" t="inlineStr">
+      <c r="I2136" s="0" t="inlineStr">
         <is>
           <t>MVD p.101</t>
         </is>
       </c>
     </row>
     <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="A2137" s="0" t="inlineStr">
         <is>
           <t>प्रयुक्ति</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2137" s="0" t="inlineStr">
         <is>
           <t>usage/application</t>
         </is>
       </c>
-      <c r="C2137" t="inlineStr">
+      <c r="C2137" s="0" t="inlineStr">
         <is>
           <t>prayukti</t>
         </is>
       </c>
-      <c r="F2137" t="inlineStr">
+      <c r="F2137" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Denotes the employment or application of a गुण (property) or साधन (means); e.g. the usage of every property is solely for creation, sustainment, or dissolution.</t>
         </is>
       </c>
-      <c r="I2137" t="inlineStr">
+      <c r="I2137" s="0" t="inlineStr">
         <is>
           <t>MVD p.112</t>
         </is>
       </c>
     </row>
     <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="A2138" s="0" t="inlineStr">
         <is>
           <t>दत्त</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2138" s="0" t="inlineStr">
         <is>
           <t>conferred</t>
         </is>
       </c>
-      <c r="C2138" t="inlineStr">
+      <c r="C2138" s="0" t="inlineStr">
         <is>
           <t>datta</t>
         </is>
       </c>
-      <c r="F2138" t="inlineStr">
+      <c r="F2138" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Technical suffix marking the source of a right/duty, as in व्यवस्था-दत्त अधिकार (orderliness-conferred rights) and कुटुंब-दत्त अधिकार (family-conferred rights).</t>
         </is>
       </c>
-      <c r="I2138" t="inlineStr">
+      <c r="I2138" s="0" t="inlineStr">
         <is>
           <t>MVD p.191</t>
         </is>
       </c>
     </row>
     <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="A2139" s="0" t="inlineStr">
         <is>
           <t>अवसरवादी</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2139" s="0" t="inlineStr">
         <is>
           <t>opportunistic</t>
         </is>
       </c>
-      <c r="C2139" t="inlineStr">
+      <c r="C2139" s="0" t="inlineStr">
         <is>
           <t>avsarwadi</t>
         </is>
       </c>
-      <c r="F2139" t="inlineStr">
+      <c r="F2139" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Paired antonym of न्यायवादी (justice-oriented); denotes opportunism-driven policy, thought, or behaviour throughout the ethics/politics discussion.</t>
         </is>
       </c>
-      <c r="I2139" t="inlineStr">
+      <c r="I2139" s="0" t="inlineStr">
         <is>
           <t>MVD p.169</t>
         </is>
       </c>
     </row>
     <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="A2140" s="0" t="inlineStr">
         <is>
           <t>न्यायवादी</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2140" s="0" t="inlineStr">
         <is>
           <t>justice-oriented/just</t>
         </is>
       </c>
-      <c r="C2140" t="inlineStr">
+      <c r="C2140" s="0" t="inlineStr">
         <is>
           <t>nyayvadi</t>
         </is>
       </c>
-      <c r="F2140" t="inlineStr">
+      <c r="F2140" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Paired antonym of अवसरवादी; denotes justice-driven policy, thought, or behaviour (e.g. 'just behaviour', 'just policy').</t>
         </is>
       </c>
-      <c r="I2140" t="inlineStr">
+      <c r="I2140" s="0" t="inlineStr">
         <is>
           <t>MVD p.222</t>
         </is>
       </c>
     </row>
     <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="A2141" s="0" t="inlineStr">
         <is>
           <t>वियोग</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2141" s="0" t="inlineStr">
         <is>
           <t>separation</t>
         </is>
       </c>
-      <c r="C2141" t="inlineStr">
+      <c r="C2141" s="0" t="inlineStr">
         <is>
           <t>viyog</t>
         </is>
       </c>
-      <c r="F2141" t="inlineStr">
+      <c r="F2141" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Central to the text's definition of धर्म: 'that which cannot be separated, or whose separation is not possible, from a unit, is its dharma'; also used for loss (of societal status).</t>
         </is>
       </c>
-      <c r="I2141" t="inlineStr">
+      <c r="I2141" s="0" t="inlineStr">
         <is>
           <t>MVD p.254</t>
         </is>
       </c>
     </row>
     <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="A2142" s="0" t="inlineStr">
         <is>
           <t>पुत्र-पुत्री</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2142" s="0" t="inlineStr">
         <is>
           <t>Son-Daughter</t>
         </is>
       </c>
-      <c r="C2142" t="inlineStr">
+      <c r="C2142" s="0" t="inlineStr">
         <is>
           <t>putra-putri</t>
         </is>
       </c>
-      <c r="F2142" t="inlineStr">
+      <c r="F2142" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] One of the ten formally defined family relationships (संबंध) with its own duty definition: acceptance of parents as having given birth and being complementary for awakening.</t>
         </is>
       </c>
-      <c r="I2142" t="inlineStr">
+      <c r="I2142" s="0" t="inlineStr">
         <is>
           <t>MVD p.341</t>
         </is>
       </c>
     </row>
     <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="A2143" s="0" t="inlineStr">
         <is>
           <t>भाई-बहन</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2143" s="0" t="inlineStr">
         <is>
           <t>Brother-Sister</t>
         </is>
       </c>
-      <c r="C2143" t="inlineStr">
+      <c r="C2143" s="0" t="inlineStr">
         <is>
           <t>bhai-bahan</t>
         </is>
       </c>
-      <c r="F2143" t="inlineStr">
+      <c r="F2143" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Another of the ten defined family relationships, with life-success defined as hope and endeavour for each other's awakening and fulfilling responsibilities with affection.</t>
         </is>
       </c>
-      <c r="I2143" t="inlineStr">
+      <c r="I2143" s="0" t="inlineStr">
         <is>
           <t>MVD p.258</t>
         </is>
       </c>
     </row>
     <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="A2144" s="0" t="inlineStr">
         <is>
           <t>अंधकार</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2144" s="0" t="inlineStr">
         <is>
           <t>darkness</t>
         </is>
       </c>
-      <c r="C2144" t="inlineStr">
+      <c r="C2144" s="0" t="inlineStr">
         <is>
           <t>andhakar</t>
         </is>
       </c>
-      <c r="F2144" t="inlineStr">
+      <c r="F2144" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Technically defined in the physics-of-matter discussion as equivalent to shadow (अंधकार मूलतः छाया ही है), part of a transparency/translucence/opacity property set.</t>
         </is>
       </c>
-      <c r="I2144" t="inlineStr">
+      <c r="I2144" s="0" t="inlineStr">
         <is>
           <t>MVD p.197</t>
         </is>
       </c>
     </row>
     <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="A2145" s="0" t="inlineStr">
         <is>
           <t>बाह्य विरोध</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2145" s="0" t="inlineStr">
         <is>
           <t>external contradiction</t>
         </is>
       </c>
-      <c r="C2145" t="inlineStr">
+      <c r="C2145" s="0" t="inlineStr">
         <is>
           <t>bahya virodh</t>
         </is>
       </c>
-      <c r="F2145" t="inlineStr">
+      <c r="F2145" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Paired opposite of the already-glossed अंतर्विरोध (internal contradiction/conflict), used in the critique of dialectical materialism's dichotomy of internal vs. external contradiction.</t>
         </is>
       </c>
-      <c r="I2145" t="inlineStr">
+      <c r="I2145" s="0" t="inlineStr">
         <is>
           <t>SB p.13</t>
         </is>
       </c>
     </row>
     <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="A2146" s="0" t="inlineStr">
         <is>
           <t>शिलायुग</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2146" s="0" t="inlineStr">
         <is>
           <t>Stone Age</t>
         </is>
       </c>
-      <c r="C2146" t="inlineStr">
+      <c r="C2146" s="0" t="inlineStr">
         <is>
           <t>shilayug</t>
         </is>
       </c>
-      <c r="F2146" t="inlineStr">
+      <c r="F2146" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Named era in the corpus's periodization of human tradition (jungle/stone age preceding metal age, clan age, village age, submission age, struggle age); consistently rendered 'Stone Age'.</t>
         </is>
       </c>
-      <c r="I2146" t="inlineStr">
+      <c r="I2146" s="0" t="inlineStr">
         <is>
           <t>SB p.28</t>
         </is>
       </c>
     </row>
     <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="A2147" s="0" t="inlineStr">
         <is>
           <t>मानवेत्तर, मानवेतर, मनुष्येत्तर</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2147" s="0" t="inlineStr">
         <is>
           <t>nature other than human / non-human (nature)</t>
         </is>
       </c>
-      <c r="C2147" t="inlineStr">
+      <c r="C2147" s="0" t="inlineStr">
         <is>
           <t>manavetar</t>
         </is>
       </c>
-      <c r="F2147" t="inlineStr">
+      <c r="F2147" s="0" t="inlineStr">
         <is>
           <t>[New row added 2026-07-08 from MVD/SB reconciliation.] Merged spelling variants (मानवेत्तर/मानवेतर/मनुष्येत्तर all attested) for the compound मानव+इतर denoting matter/plant/animal orders collectively, as distinct from the human/knowledge order. Coined compound (मानव+इतर) referring to the material/biological/animal orders collectively as distinct from the human/knowledge order; rendered contextually as 'animals', 'the rest of nature', or 'nature other than humans' (MVD p.55: 'capable of use... of the rest of nature'; SB p.15: 'nature other than humans').; Denotes the whole of nature excluding humans (matter, plants, animals) as a category distinct from the human/knowledge order, e.g. 'मनुष्येत्तर संपूर्ण प्रकृति' rendered as 'the entire nature apart from humans'.</t>
         </is>
       </c>
-      <c r="I2147" t="inlineStr">
+      <c r="I2147" s="0" t="inlineStr">
         <is>
           <t>SB p.15; SB p.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>अखण्ड</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>undivided</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>akhand</t>
+        </is>
+      </c>
+      <c r="F2148" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अखण्ड सामाजिकता / अखण्ड समाज = undivided sociality / undivided society (MVD).</t>
+        </is>
+      </c>
+      <c r="I2148" t="inlineStr">
+        <is>
+          <t>MVD p.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>पूरक</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>complementary</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>purak</t>
+        </is>
+      </c>
+      <c r="F2149" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: एकसूत्रता = being helpful and complementary for mutual awakening.</t>
+        </is>
+      </c>
+      <c r="I2149" t="inlineStr">
+        <is>
+          <t>MVD p.102</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>जंगल युग</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>Jungle Age</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>jangal yug</t>
+        </is>
+      </c>
+      <c r="F2150" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: SB periodization Jungle Age → Stone Age → Iron Age → Submission Age → Struggle Age.</t>
+        </is>
+      </c>
+      <c r="I2150" t="inlineStr">
+        <is>
+          <t>SB p.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>भाषा</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>bhasha</t>
+        </is>
+      </c>
+      <c r="F2151" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: व्यवहार, भाव व भाषा = behaviour, sentiments, and language.</t>
+        </is>
+      </c>
+      <c r="I2151" t="inlineStr">
+        <is>
+          <t>MVD p.229</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>अवसर</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>opportunity / opportunism (contextual)</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>avsar</t>
+        </is>
+      </c>
+      <c r="F2152" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: bare अवसर often 'opportunity'; in न्याय तथा अवसर भेद paired with opportunism (cf. अवसरवादी).</t>
+        </is>
+      </c>
+      <c r="I2152" t="inlineStr">
+        <is>
+          <t>MVD p.213</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>वर्ग</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>varg</t>
+        </is>
+      </c>
+      <c r="F2153" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: जाति, वर्ग, मत, सम्प्रदाय = castes, classes, beliefs, and sects.</t>
+        </is>
+      </c>
+      <c r="I2153" t="inlineStr">
+        <is>
+          <t>MVD p.267</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>विपरीत</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>opposite / contrary</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>viparit</t>
+        </is>
+      </c>
+      <c r="F2154" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: इसके विपरीत = in contrast / opposite (e.g. दया vs द्वेष).</t>
+        </is>
+      </c>
+      <c r="I2154" t="inlineStr">
+        <is>
+          <t>MVD p.189</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>अल्प चेतन</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>partially conscious / partially awakened</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>alp chetan</t>
+        </is>
+      </c>
+      <c r="F2155" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अल्प चेतन in the fivefold consciousness scale = partially conscious / partially awakened.</t>
+        </is>
+      </c>
+      <c r="I2155" t="inlineStr">
+        <is>
+          <t>MVD p.274</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>अविकसित</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>undeveloped</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>aviksit</t>
+        </is>
+      </c>
+      <c r="F2156" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अविकसित इकाई = undeveloped unit (contrast विकसित).</t>
+        </is>
+      </c>
+      <c r="I2156" t="inlineStr">
+        <is>
+          <t>MVD p.290</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>बन्धन</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>bondage</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>bandhan</t>
+        </is>
+      </c>
+      <c r="F2157" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: mirage and delusion which is bondage.</t>
+        </is>
+      </c>
+      <c r="I2157" t="inlineStr">
+        <is>
+          <t>MVD p.140</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>मार्ग</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>marg</t>
+        </is>
+      </c>
+      <c r="F2158" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: मार्ग प्रशस्त = pave the path (moral policy).</t>
+        </is>
+      </c>
+      <c r="I2158" t="inlineStr">
+        <is>
+          <t>MVD p.243</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>श्रेष्ठ</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>superior</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>shreshth</t>
+        </is>
+      </c>
+      <c r="F2159" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: स्व… को श्रेष्ठ तथा अन्य को नेष्ट = one's own as superior, others as inferior (conceit).</t>
+        </is>
+      </c>
+      <c r="I2159" t="inlineStr">
+        <is>
+          <t>MVD p.185</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>समर्थन</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>endorsement / support</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>samarthan</t>
+        </is>
+      </c>
+      <c r="F2160" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: समर्थन व पालन = endorsing and adhering.</t>
+        </is>
+      </c>
+      <c r="I2160" t="inlineStr">
+        <is>
+          <t>MVD p.257</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>सर्वमानव</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>all humans</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>sarvamanav</t>
+        </is>
+      </c>
+      <c r="F2161" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: सर्वमानव में, से, के लिए = in, by, and for all humans.</t>
+        </is>
+      </c>
+      <c r="I2161" t="inlineStr">
+        <is>
+          <t>MVD p.300</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>अर्ध चेतन</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>half-conscious / half-awakened</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>ardh chetan</t>
+        </is>
+      </c>
+      <c r="F2162" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अर्ध चेतन in the fivefold consciousness scale.</t>
+        </is>
+      </c>
+      <c r="I2162" t="inlineStr">
+        <is>
+          <t>MVD p.274</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>द्योतक</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>indicative</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>dyotak</t>
+        </is>
+      </c>
+      <c r="F2163" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: मानवीयता का द्योतक = indicative of humaneness.</t>
+        </is>
+      </c>
+      <c r="I2163" t="inlineStr">
+        <is>
+          <t>MVD p.176</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>नस्ल</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>nasl</t>
+        </is>
+      </c>
+      <c r="F2164" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: रंग और नस्ल = colour and race (SB).</t>
+        </is>
+      </c>
+      <c r="I2164" t="inlineStr">
+        <is>
+          <t>SB p.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>माता-पिता</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>mother-father / parents</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>mata-pita</t>
+        </is>
+      </c>
+      <c r="F2165" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: one of the defined family relationships; life of a parent.</t>
+        </is>
+      </c>
+      <c r="I2165" t="inlineStr">
+        <is>
+          <t>MVD p.257</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>पिता</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>father / parent</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>pita</t>
+        </is>
+      </c>
+      <c r="F2166" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: see माता-पिता row; parental relationship definition.</t>
+        </is>
+      </c>
+      <c r="I2166" t="inlineStr">
+        <is>
+          <t>MVD p.257</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>मौलिक</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>fundamental</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>maulik</t>
+        </is>
+      </c>
+      <c r="F2167" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: मौलिक मूल्य = fundamental value (gratitude).</t>
+        </is>
+      </c>
+      <c r="I2167" t="inlineStr">
+        <is>
+          <t>MVD p.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>संभावना</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>possibility</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>sambhavna</t>
+        </is>
+      </c>
+      <c r="F2168" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: तृप्ति की संभावना = possibility of satisfaction.</t>
+        </is>
+      </c>
+      <c r="I2168" t="inlineStr">
+        <is>
+          <t>MVD p.166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>दिशा</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>disha</t>
+        </is>
+      </c>
+      <c r="F2169" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: दिशा निर्धारण = determining the direction (science/vigyan).</t>
+        </is>
+      </c>
+      <c r="I2169" t="inlineStr">
+        <is>
+          <t>MVD p.170</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>भूमि</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>Earth / land</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>bhumi</t>
+        </is>
+      </c>
+      <c r="F2170" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: भूमि स्वर्ग हो = May the Earth be heavenly.</t>
+        </is>
+      </c>
+      <c r="I2170" t="inlineStr">
+        <is>
+          <t>MVD p.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>पालन</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>adherence / observance</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>palan</t>
+        </is>
+      </c>
+      <c r="F2171" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: समर्थन व पालन = endorsing and adhering.</t>
+        </is>
+      </c>
+      <c r="I2171" t="inlineStr">
+        <is>
+          <t>MVD p.257</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>आधारित</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>based on</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>adharit</t>
+        </is>
+      </c>
+      <c r="F2172" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: श्रम मूल्य… आधारित = based on evaluation and exchange of labour.</t>
+        </is>
+      </c>
+      <c r="I2172" t="inlineStr">
+        <is>
+          <t>MVD p.269</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>समुदाय, समुदायों</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>community / communities</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>samuday</t>
+        </is>
+      </c>
+      <c r="F2173" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: human communities formed around freedom from fear.</t>
+        </is>
+      </c>
+      <c r="I2173" t="inlineStr">
+        <is>
+          <t>MVD p.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>अमानवीय दृष्टि</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>inhumane perspective</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>amanviya drishti</t>
+        </is>
+      </c>
+      <c r="F2174" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: explicit MVD gloss Inhumane Perspective (amanveeya drishti).</t>
+        </is>
+      </c>
+      <c r="I2174" t="inlineStr">
+        <is>
+          <t>MVD p.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>असंतुलन</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>imbalance / disparity</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>asantulan</t>
+        </is>
+      </c>
+      <c r="F2175" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अमीरी-गरीबी का असंतुलन = disparity between rich and poor.</t>
+        </is>
+      </c>
+      <c r="I2175" t="inlineStr">
+        <is>
+          <t>MVD p.267</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>आर्थिक सुरक्षा</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>economic security</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>arthik suraksha</t>
+        </is>
+      </c>
+      <c r="F2176" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: explicit MVD heading Economic Security.</t>
+        </is>
+      </c>
+      <c r="I2176" t="inlineStr">
+        <is>
+          <t>MVD p.265</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>इकाईयाँ</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>ikaiyan</t>
+        </is>
+      </c>
+      <c r="F2177" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: इकाईयाँ अनंत = units are countless.</t>
+        </is>
+      </c>
+      <c r="I2177" t="inlineStr">
+        <is>
+          <t>MVD p.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>नियंत्रित, नियन्त्रण</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>regulated / regulation</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>niyantrit</t>
+        </is>
+      </c>
+      <c r="F2178" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: प्रकृति नियंत्रित एवं संरक्षित = nature regulated and conserved; नियन्त्रण = regulation of prana.</t>
+        </is>
+      </c>
+      <c r="I2178" t="inlineStr">
+        <is>
+          <t>MVD p.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>पृथ्वी</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>prithvi</t>
+        </is>
+      </c>
+      <c r="F2179" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: Geography is study of the Earth's structure.</t>
+        </is>
+      </c>
+      <c r="I2179" t="inlineStr">
+        <is>
+          <t>MVD p.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>शाकाहारी</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>herbivorous</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>shakahari</t>
+        </is>
+      </c>
+      <c r="F2180" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: शाकाहारी और मांसाहारी = herbivorous and carnivorous.</t>
+        </is>
+      </c>
+      <c r="I2180" t="inlineStr">
+        <is>
+          <t>SB p.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>मांसाहारी</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>carnivorous</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>mansahari</t>
+        </is>
+      </c>
+      <c r="F2181" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: paired with शाकाहारी in SB animal-order discussion.</t>
+        </is>
+      </c>
+      <c r="I2181" t="inlineStr">
+        <is>
+          <t>SB p.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>सम्पर्क</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>association / contact</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>sampark</t>
+        </is>
+      </c>
+      <c r="F2182" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: सम्पर्क एवं संबंध = associations and relationships (paired with संबंध).</t>
+        </is>
+      </c>
+      <c r="I2182" t="inlineStr">
+        <is>
+          <t>MVD p.242</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>स्वर्ग</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>heaven / heavenly</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>svarg</t>
+        </is>
+      </c>
+      <c r="F2183" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: भूमि स्वर्ग हो = May the Earth be heavenly.</t>
+        </is>
+      </c>
+      <c r="I2183" t="inlineStr">
+        <is>
+          <t>MVD p.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>अधिकतम</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>maximum</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>adhiktam</t>
+        </is>
+      </c>
+      <c r="F2184" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: अधिकतम श्रम = maximum effort.</t>
+        </is>
+      </c>
+      <c r="I2184" t="inlineStr">
+        <is>
+          <t>MVD p.266</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>निरन्तरता</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>continuity</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>nirantarta</t>
+        </is>
+      </c>
+      <c r="F2185" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: कृतज्ञता की निरन्तरता = continuity of gratitude.</t>
+        </is>
+      </c>
+      <c r="I2185" t="inlineStr">
+        <is>
+          <t>MVD p.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>स्व पुरुष</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>one's husband / marital faithfulness (contextual)</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>sva purush</t>
+        </is>
+      </c>
+      <c r="F2186" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: स्वनारी/स्व पुरुष in the righteous-wealth / marital-faithfulness policy triad.</t>
+        </is>
+      </c>
+      <c r="I2186" t="inlineStr">
+        <is>
+          <t>MVD p.267</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>प्रवृत्ति, प्रवृत्तियाँ</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>tendency / tendencies</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>pravritti</t>
+        </is>
+      </c>
+      <c r="F2187" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: विचार व प्रवृत्तियाँ = thoughts and tendencies.</t>
+        </is>
+      </c>
+      <c r="I2187" t="inlineStr">
+        <is>
+          <t>MVD p.211</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>प्रसन्नता</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>happiness / gladly</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>prasannata</t>
+        </is>
+      </c>
+      <c r="F2188" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: प्रसन्नता पूर्वक = happily (generosity definition).</t>
+        </is>
+      </c>
+      <c r="I2188" t="inlineStr">
+        <is>
+          <t>MVD p.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>मनुष्य</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>human / humans</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>manushya</t>
+        </is>
+      </c>
+      <c r="F2189" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: मनुष्य देवता हो = May humans be deities.</t>
+        </is>
+      </c>
+      <c r="I2189" t="inlineStr">
+        <is>
+          <t>MVD p.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>वर्ग विहीन</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>classless</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>varg vihin</t>
+        </is>
+      </c>
+      <c r="F2190" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: वर्ग विहीन समाज = classless society.</t>
+        </is>
+      </c>
+      <c r="I2190" t="inlineStr">
+        <is>
+          <t>MVD p.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>वैयक्तिक</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>vaiyaktik</t>
+        </is>
+      </c>
+      <c r="F2191" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: वैयक्तिक जीवन व जीविका = individual life and livelihood.</t>
+        </is>
+      </c>
+      <c r="I2191" t="inlineStr">
+        <is>
+          <t>MVD p.168</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>संरक्षित</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>protected / conserved</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>sanrakshit</t>
+        </is>
+      </c>
+      <c r="F2192" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: नियंत्रित तथा संरक्षित = regulated and protected/conserved.</t>
+        </is>
+      </c>
+      <c r="I2192" t="inlineStr">
+        <is>
+          <t>MVD p.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>योग्य</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>fit / worthy / suitable</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>yogya</t>
+        </is>
+      </c>
+      <c r="F2193" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: योगानुभूति योग्य विकास = development fit for realisation of yog; distinct from योग्यता (ability).</t>
+        </is>
+      </c>
+      <c r="I2193" t="inlineStr">
+        <is>
+          <t>MVD p.165</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>सुलभ</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>accessible</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>sulabh</t>
+        </is>
+      </c>
+      <c r="F2194" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: समाधान व समझ सुलभ = resolution and understanding become accessible.</t>
+        </is>
+      </c>
+      <c r="I2194" t="inlineStr">
+        <is>
+          <t>MVD p.290</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>संभव</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>sambhav</t>
+        </is>
+      </c>
+      <c r="F2195" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: …से ही संभव है = is possible only through…</t>
+        </is>
+      </c>
+      <c r="I2195" t="inlineStr">
+        <is>
+          <t>MVD p.172</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>स्थान</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>place / position</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>sthan</t>
+        </is>
+      </c>
+      <c r="F2196" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: महत्वपूर्ण स्थान = significant position/place.</t>
+        </is>
+      </c>
+      <c r="I2196" t="inlineStr">
+        <is>
+          <t>MVD p.192</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>स्वरुप, स्वरूप</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>form / aspect</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>svarup</t>
+        </is>
+      </c>
+      <c r="F2197" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: तीन स्वरुप में = under three headings/forms (theism categories).</t>
+        </is>
+      </c>
+      <c r="I2197" t="inlineStr">
+        <is>
+          <t>SB p.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>नारी</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>woman / wife (contextual)</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>nari</t>
+        </is>
+      </c>
+      <c r="F2198" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: स्व-नारी/पर-नारी in marital faithfulness vs adultery discussion.</t>
+        </is>
+      </c>
+      <c r="I2198" t="inlineStr">
+        <is>
+          <t>MVD p.189</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>इंगित</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>indicated / signalled</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>ingit</t>
+        </is>
+      </c>
+      <c r="F2199" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: इंगित होने वाले सम्पूर्ण संकेतों = all the signals indicated/received.</t>
+        </is>
+      </c>
+      <c r="I2199" t="inlineStr">
+        <is>
+          <t>MVD p.345</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>उपलब्ध</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>available / allocated</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>upalabdh</t>
+        </is>
+      </c>
+      <c r="F2200" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: साधन उपलब्ध कराना = allocating/making resources available.</t>
+        </is>
+      </c>
+      <c r="I2200" t="inlineStr">
+        <is>
+          <t>MVD p.268</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>वृत्ति, वृति</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>vritti</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>vritti</t>
+        </is>
+      </c>
+      <c r="F2201" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: kept as vritti in MVD English (mun → vritti → chitta → buddhi hierarchy).</t>
+        </is>
+      </c>
+      <c r="I2201" t="inlineStr">
+        <is>
+          <t>MVD p.286</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>संदर्भ</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>context / respect (with respect to)</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>sandarbh</t>
+        </is>
+      </c>
+      <c r="F2202" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: मानव के संदर्भ में = with respect to humans.</t>
+        </is>
+      </c>
+      <c r="I2202" t="inlineStr">
+        <is>
+          <t>MVD p.231</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>क्षतिग्रस्त</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>damaged / destroyed</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>kshatigrast</t>
+        </is>
+      </c>
+      <c r="F2203" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: सर्वाधिक क्षतिग्रस्त = maximum destruction/damage to nature.</t>
+        </is>
+      </c>
+      <c r="I2203" t="inlineStr">
+        <is>
+          <t>SB p.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>रहस्यमय</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>mysterious</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>rahasyamay</t>
+        </is>
+      </c>
+      <c r="F2204" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: रहस्यमय लगता है = may seem mysterious.</t>
+        </is>
+      </c>
+      <c r="I2204" t="inlineStr">
+        <is>
+          <t>MVD p.295</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>समाहित</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>encompassed / included</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>samahit</t>
+        </is>
+      </c>
+      <c r="F2205" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: व्यापक में समाहित = encompassed within omnipresence.</t>
+        </is>
+      </c>
+      <c r="I2205" t="inlineStr">
+        <is>
+          <t>MVD p.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>स्वाभाविक</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>natural / typically</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>svabhavik</t>
+        </is>
+      </c>
+      <c r="F2206" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: typically/naturally occurs (brother-sister recognition).</t>
+        </is>
+      </c>
+      <c r="I2206" t="inlineStr">
+        <is>
+          <t>MVD p.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>धातु युग</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>Iron Age</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>dhatu yug</t>
+        </is>
+      </c>
+      <c r="F2207" t="inlineStr">
+        <is>
+          <t>Phase 4 curated: SB periodization Stone Age to Iron Age (धातु युग).</t>
+        </is>
+      </c>
+      <c r="I2207" t="inlineStr">
+        <is>
+          <t>SB p.23</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2207"/>
+  <dimension ref="A1:K2242"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.44" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="23.22" customWidth="1" style="114" min="1" max="1"/>
@@ -58181,1622 +58181,2567 @@
       </c>
     </row>
     <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="A2148" s="0" t="inlineStr">
         <is>
           <t>अखण्ड</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2148" s="0" t="inlineStr">
         <is>
           <t>undivided</t>
         </is>
       </c>
-      <c r="C2148" t="inlineStr">
+      <c r="C2148" s="0" t="inlineStr">
         <is>
           <t>akhand</t>
         </is>
       </c>
-      <c r="F2148" t="inlineStr">
+      <c r="F2148" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अखण्ड सामाजिकता / अखण्ड समाज = undivided sociality / undivided society (MVD).</t>
         </is>
       </c>
-      <c r="I2148" t="inlineStr">
+      <c r="I2148" s="0" t="inlineStr">
         <is>
           <t>MVD p.15</t>
         </is>
       </c>
     </row>
     <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="A2149" s="0" t="inlineStr">
         <is>
           <t>पूरक</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2149" s="0" t="inlineStr">
         <is>
           <t>complementary</t>
         </is>
       </c>
-      <c r="C2149" t="inlineStr">
+      <c r="C2149" s="0" t="inlineStr">
         <is>
           <t>purak</t>
         </is>
       </c>
-      <c r="F2149" t="inlineStr">
+      <c r="F2149" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: एकसूत्रता = being helpful and complementary for mutual awakening.</t>
         </is>
       </c>
-      <c r="I2149" t="inlineStr">
+      <c r="I2149" s="0" t="inlineStr">
         <is>
           <t>MVD p.102</t>
         </is>
       </c>
     </row>
     <row r="2150">
-      <c r="A2150" t="inlineStr">
+      <c r="A2150" s="0" t="inlineStr">
         <is>
           <t>जंगल युग</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2150" s="0" t="inlineStr">
         <is>
           <t>Jungle Age</t>
         </is>
       </c>
-      <c r="C2150" t="inlineStr">
+      <c r="C2150" s="0" t="inlineStr">
         <is>
           <t>jangal yug</t>
         </is>
       </c>
-      <c r="F2150" t="inlineStr">
+      <c r="F2150" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: SB periodization Jungle Age → Stone Age → Iron Age → Submission Age → Struggle Age.</t>
         </is>
       </c>
-      <c r="I2150" t="inlineStr">
+      <c r="I2150" s="0" t="inlineStr">
         <is>
           <t>SB p.23</t>
         </is>
       </c>
     </row>
     <row r="2151">
-      <c r="A2151" t="inlineStr">
+      <c r="A2151" s="0" t="inlineStr">
         <is>
           <t>भाषा</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2151" s="0" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C2151" t="inlineStr">
+      <c r="C2151" s="0" t="inlineStr">
         <is>
           <t>bhasha</t>
         </is>
       </c>
-      <c r="F2151" t="inlineStr">
+      <c r="F2151" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: व्यवहार, भाव व भाषा = behaviour, sentiments, and language.</t>
         </is>
       </c>
-      <c r="I2151" t="inlineStr">
+      <c r="I2151" s="0" t="inlineStr">
         <is>
           <t>MVD p.229</t>
         </is>
       </c>
     </row>
     <row r="2152">
-      <c r="A2152" t="inlineStr">
+      <c r="A2152" s="0" t="inlineStr">
         <is>
           <t>अवसर</t>
         </is>
       </c>
-      <c r="B2152" t="inlineStr">
+      <c r="B2152" s="0" t="inlineStr">
         <is>
           <t>opportunity / opportunism (contextual)</t>
         </is>
       </c>
-      <c r="C2152" t="inlineStr">
+      <c r="C2152" s="0" t="inlineStr">
         <is>
           <t>avsar</t>
         </is>
       </c>
-      <c r="F2152" t="inlineStr">
+      <c r="F2152" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: bare अवसर often 'opportunity'; in न्याय तथा अवसर भेद paired with opportunism (cf. अवसरवादी).</t>
         </is>
       </c>
-      <c r="I2152" t="inlineStr">
+      <c r="I2152" s="0" t="inlineStr">
         <is>
           <t>MVD p.213</t>
         </is>
       </c>
     </row>
     <row r="2153">
-      <c r="A2153" t="inlineStr">
+      <c r="A2153" s="0" t="inlineStr">
         <is>
           <t>वर्ग</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2153" s="0" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C2153" t="inlineStr">
+      <c r="C2153" s="0" t="inlineStr">
         <is>
           <t>varg</t>
         </is>
       </c>
-      <c r="F2153" t="inlineStr">
+      <c r="F2153" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: जाति, वर्ग, मत, सम्प्रदाय = castes, classes, beliefs, and sects.</t>
         </is>
       </c>
-      <c r="I2153" t="inlineStr">
+      <c r="I2153" s="0" t="inlineStr">
         <is>
           <t>MVD p.267</t>
         </is>
       </c>
     </row>
     <row r="2154">
-      <c r="A2154" t="inlineStr">
+      <c r="A2154" s="0" t="inlineStr">
         <is>
           <t>विपरीत</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2154" s="0" t="inlineStr">
         <is>
           <t>opposite / contrary</t>
         </is>
       </c>
-      <c r="C2154" t="inlineStr">
+      <c r="C2154" s="0" t="inlineStr">
         <is>
           <t>viparit</t>
         </is>
       </c>
-      <c r="F2154" t="inlineStr">
+      <c r="F2154" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: इसके विपरीत = in contrast / opposite (e.g. दया vs द्वेष).</t>
         </is>
       </c>
-      <c r="I2154" t="inlineStr">
+      <c r="I2154" s="0" t="inlineStr">
         <is>
           <t>MVD p.189</t>
         </is>
       </c>
     </row>
     <row r="2155">
-      <c r="A2155" t="inlineStr">
+      <c r="A2155" s="0" t="inlineStr">
         <is>
           <t>अल्प चेतन</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2155" s="0" t="inlineStr">
         <is>
           <t>partially conscious / partially awakened</t>
         </is>
       </c>
-      <c r="C2155" t="inlineStr">
+      <c r="C2155" s="0" t="inlineStr">
         <is>
           <t>alp chetan</t>
         </is>
       </c>
-      <c r="F2155" t="inlineStr">
+      <c r="F2155" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अल्प चेतन in the fivefold consciousness scale = partially conscious / partially awakened.</t>
         </is>
       </c>
-      <c r="I2155" t="inlineStr">
+      <c r="I2155" s="0" t="inlineStr">
         <is>
           <t>MVD p.274</t>
         </is>
       </c>
     </row>
     <row r="2156">
-      <c r="A2156" t="inlineStr">
+      <c r="A2156" s="0" t="inlineStr">
         <is>
           <t>अविकसित</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2156" s="0" t="inlineStr">
         <is>
           <t>undeveloped</t>
         </is>
       </c>
-      <c r="C2156" t="inlineStr">
+      <c r="C2156" s="0" t="inlineStr">
         <is>
           <t>aviksit</t>
         </is>
       </c>
-      <c r="F2156" t="inlineStr">
+      <c r="F2156" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अविकसित इकाई = undeveloped unit (contrast विकसित).</t>
         </is>
       </c>
-      <c r="I2156" t="inlineStr">
+      <c r="I2156" s="0" t="inlineStr">
         <is>
           <t>MVD p.290</t>
         </is>
       </c>
     </row>
     <row r="2157">
-      <c r="A2157" t="inlineStr">
+      <c r="A2157" s="0" t="inlineStr">
         <is>
           <t>बन्धन</t>
         </is>
       </c>
-      <c r="B2157" t="inlineStr">
+      <c r="B2157" s="0" t="inlineStr">
         <is>
           <t>bondage</t>
         </is>
       </c>
-      <c r="C2157" t="inlineStr">
+      <c r="C2157" s="0" t="inlineStr">
         <is>
           <t>bandhan</t>
         </is>
       </c>
-      <c r="F2157" t="inlineStr">
+      <c r="F2157" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: mirage and delusion which is bondage.</t>
         </is>
       </c>
-      <c r="I2157" t="inlineStr">
+      <c r="I2157" s="0" t="inlineStr">
         <is>
           <t>MVD p.140</t>
         </is>
       </c>
     </row>
     <row r="2158">
-      <c r="A2158" t="inlineStr">
+      <c r="A2158" s="0" t="inlineStr">
         <is>
           <t>मार्ग</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2158" s="0" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="C2158" t="inlineStr">
+      <c r="C2158" s="0" t="inlineStr">
         <is>
           <t>marg</t>
         </is>
       </c>
-      <c r="F2158" t="inlineStr">
+      <c r="F2158" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: मार्ग प्रशस्त = pave the path (moral policy).</t>
         </is>
       </c>
-      <c r="I2158" t="inlineStr">
+      <c r="I2158" s="0" t="inlineStr">
         <is>
           <t>MVD p.243</t>
         </is>
       </c>
     </row>
     <row r="2159">
-      <c r="A2159" t="inlineStr">
+      <c r="A2159" s="0" t="inlineStr">
         <is>
           <t>श्रेष्ठ</t>
         </is>
       </c>
-      <c r="B2159" t="inlineStr">
+      <c r="B2159" s="0" t="inlineStr">
         <is>
           <t>superior</t>
         </is>
       </c>
-      <c r="C2159" t="inlineStr">
+      <c r="C2159" s="0" t="inlineStr">
         <is>
           <t>shreshth</t>
         </is>
       </c>
-      <c r="F2159" t="inlineStr">
+      <c r="F2159" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: स्व… को श्रेष्ठ तथा अन्य को नेष्ट = one's own as superior, others as inferior (conceit).</t>
         </is>
       </c>
-      <c r="I2159" t="inlineStr">
+      <c r="I2159" s="0" t="inlineStr">
         <is>
           <t>MVD p.185</t>
         </is>
       </c>
     </row>
     <row r="2160">
-      <c r="A2160" t="inlineStr">
+      <c r="A2160" s="0" t="inlineStr">
         <is>
           <t>समर्थन</t>
         </is>
       </c>
-      <c r="B2160" t="inlineStr">
+      <c r="B2160" s="0" t="inlineStr">
         <is>
           <t>endorsement / support</t>
         </is>
       </c>
-      <c r="C2160" t="inlineStr">
+      <c r="C2160" s="0" t="inlineStr">
         <is>
           <t>samarthan</t>
         </is>
       </c>
-      <c r="F2160" t="inlineStr">
+      <c r="F2160" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: समर्थन व पालन = endorsing and adhering.</t>
         </is>
       </c>
-      <c r="I2160" t="inlineStr">
+      <c r="I2160" s="0" t="inlineStr">
         <is>
           <t>MVD p.257</t>
         </is>
       </c>
     </row>
     <row r="2161">
-      <c r="A2161" t="inlineStr">
+      <c r="A2161" s="0" t="inlineStr">
         <is>
           <t>सर्वमानव</t>
         </is>
       </c>
-      <c r="B2161" t="inlineStr">
+      <c r="B2161" s="0" t="inlineStr">
         <is>
           <t>all humans</t>
         </is>
       </c>
-      <c r="C2161" t="inlineStr">
+      <c r="C2161" s="0" t="inlineStr">
         <is>
           <t>sarvamanav</t>
         </is>
       </c>
-      <c r="F2161" t="inlineStr">
+      <c r="F2161" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: सर्वमानव में, से, के लिए = in, by, and for all humans.</t>
         </is>
       </c>
-      <c r="I2161" t="inlineStr">
+      <c r="I2161" s="0" t="inlineStr">
         <is>
           <t>MVD p.300</t>
         </is>
       </c>
     </row>
     <row r="2162">
-      <c r="A2162" t="inlineStr">
+      <c r="A2162" s="0" t="inlineStr">
         <is>
           <t>अर्ध चेतन</t>
         </is>
       </c>
-      <c r="B2162" t="inlineStr">
+      <c r="B2162" s="0" t="inlineStr">
         <is>
           <t>half-conscious / half-awakened</t>
         </is>
       </c>
-      <c r="C2162" t="inlineStr">
+      <c r="C2162" s="0" t="inlineStr">
         <is>
           <t>ardh chetan</t>
         </is>
       </c>
-      <c r="F2162" t="inlineStr">
+      <c r="F2162" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अर्ध चेतन in the fivefold consciousness scale.</t>
         </is>
       </c>
-      <c r="I2162" t="inlineStr">
+      <c r="I2162" s="0" t="inlineStr">
         <is>
           <t>MVD p.274</t>
         </is>
       </c>
     </row>
     <row r="2163">
-      <c r="A2163" t="inlineStr">
+      <c r="A2163" s="0" t="inlineStr">
         <is>
           <t>द्योतक</t>
         </is>
       </c>
-      <c r="B2163" t="inlineStr">
+      <c r="B2163" s="0" t="inlineStr">
         <is>
           <t>indicative</t>
         </is>
       </c>
-      <c r="C2163" t="inlineStr">
+      <c r="C2163" s="0" t="inlineStr">
         <is>
           <t>dyotak</t>
         </is>
       </c>
-      <c r="F2163" t="inlineStr">
+      <c r="F2163" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: मानवीयता का द्योतक = indicative of humaneness.</t>
         </is>
       </c>
-      <c r="I2163" t="inlineStr">
+      <c r="I2163" s="0" t="inlineStr">
         <is>
           <t>MVD p.176</t>
         </is>
       </c>
     </row>
     <row r="2164">
-      <c r="A2164" t="inlineStr">
+      <c r="A2164" s="0" t="inlineStr">
         <is>
           <t>नस्ल</t>
         </is>
       </c>
-      <c r="B2164" t="inlineStr">
+      <c r="B2164" s="0" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="C2164" t="inlineStr">
+      <c r="C2164" s="0" t="inlineStr">
         <is>
           <t>nasl</t>
         </is>
       </c>
-      <c r="F2164" t="inlineStr">
+      <c r="F2164" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: रंग और नस्ल = colour and race (SB).</t>
         </is>
       </c>
-      <c r="I2164" t="inlineStr">
+      <c r="I2164" s="0" t="inlineStr">
         <is>
           <t>SB p.22</t>
         </is>
       </c>
     </row>
     <row r="2165">
-      <c r="A2165" t="inlineStr">
+      <c r="A2165" s="0" t="inlineStr">
         <is>
           <t>माता-पिता</t>
         </is>
       </c>
-      <c r="B2165" t="inlineStr">
+      <c r="B2165" s="0" t="inlineStr">
         <is>
           <t>mother-father / parents</t>
         </is>
       </c>
-      <c r="C2165" t="inlineStr">
+      <c r="C2165" s="0" t="inlineStr">
         <is>
           <t>mata-pita</t>
         </is>
       </c>
-      <c r="F2165" t="inlineStr">
+      <c r="F2165" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: one of the defined family relationships; life of a parent.</t>
         </is>
       </c>
-      <c r="I2165" t="inlineStr">
+      <c r="I2165" s="0" t="inlineStr">
         <is>
           <t>MVD p.257</t>
         </is>
       </c>
     </row>
     <row r="2166">
-      <c r="A2166" t="inlineStr">
+      <c r="A2166" s="0" t="inlineStr">
         <is>
           <t>पिता</t>
         </is>
       </c>
-      <c r="B2166" t="inlineStr">
+      <c r="B2166" s="0" t="inlineStr">
         <is>
           <t>father / parent</t>
         </is>
       </c>
-      <c r="C2166" t="inlineStr">
+      <c r="C2166" s="0" t="inlineStr">
         <is>
           <t>pita</t>
         </is>
       </c>
-      <c r="F2166" t="inlineStr">
+      <c r="F2166" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: see माता-पिता row; parental relationship definition.</t>
         </is>
       </c>
-      <c r="I2166" t="inlineStr">
+      <c r="I2166" s="0" t="inlineStr">
         <is>
           <t>MVD p.257</t>
         </is>
       </c>
     </row>
     <row r="2167">
-      <c r="A2167" t="inlineStr">
+      <c r="A2167" s="0" t="inlineStr">
         <is>
           <t>मौलिक</t>
         </is>
       </c>
-      <c r="B2167" t="inlineStr">
+      <c r="B2167" s="0" t="inlineStr">
         <is>
           <t>fundamental</t>
         </is>
       </c>
-      <c r="C2167" t="inlineStr">
+      <c r="C2167" s="0" t="inlineStr">
         <is>
           <t>maulik</t>
         </is>
       </c>
-      <c r="F2167" t="inlineStr">
+      <c r="F2167" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: मौलिक मूल्य = fundamental value (gratitude).</t>
         </is>
       </c>
-      <c r="I2167" t="inlineStr">
+      <c r="I2167" s="0" t="inlineStr">
         <is>
           <t>MVD p.29</t>
         </is>
       </c>
     </row>
     <row r="2168">
-      <c r="A2168" t="inlineStr">
+      <c r="A2168" s="0" t="inlineStr">
         <is>
           <t>संभावना</t>
         </is>
       </c>
-      <c r="B2168" t="inlineStr">
+      <c r="B2168" s="0" t="inlineStr">
         <is>
           <t>possibility</t>
         </is>
       </c>
-      <c r="C2168" t="inlineStr">
+      <c r="C2168" s="0" t="inlineStr">
         <is>
           <t>sambhavna</t>
         </is>
       </c>
-      <c r="F2168" t="inlineStr">
+      <c r="F2168" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: तृप्ति की संभावना = possibility of satisfaction.</t>
         </is>
       </c>
-      <c r="I2168" t="inlineStr">
+      <c r="I2168" s="0" t="inlineStr">
         <is>
           <t>MVD p.166</t>
         </is>
       </c>
     </row>
     <row r="2169">
-      <c r="A2169" t="inlineStr">
+      <c r="A2169" s="0" t="inlineStr">
         <is>
           <t>दिशा</t>
         </is>
       </c>
-      <c r="B2169" t="inlineStr">
+      <c r="B2169" s="0" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="C2169" t="inlineStr">
+      <c r="C2169" s="0" t="inlineStr">
         <is>
           <t>disha</t>
         </is>
       </c>
-      <c r="F2169" t="inlineStr">
+      <c r="F2169" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: दिशा निर्धारण = determining the direction (science/vigyan).</t>
         </is>
       </c>
-      <c r="I2169" t="inlineStr">
+      <c r="I2169" s="0" t="inlineStr">
         <is>
           <t>MVD p.170</t>
         </is>
       </c>
     </row>
     <row r="2170">
-      <c r="A2170" t="inlineStr">
+      <c r="A2170" s="0" t="inlineStr">
         <is>
           <t>भूमि</t>
         </is>
       </c>
-      <c r="B2170" t="inlineStr">
+      <c r="B2170" s="0" t="inlineStr">
         <is>
           <t>Earth / land</t>
         </is>
       </c>
-      <c r="C2170" t="inlineStr">
+      <c r="C2170" s="0" t="inlineStr">
         <is>
           <t>bhumi</t>
         </is>
       </c>
-      <c r="F2170" t="inlineStr">
+      <c r="F2170" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: भूमि स्वर्ग हो = May the Earth be heavenly.</t>
         </is>
       </c>
-      <c r="I2170" t="inlineStr">
+      <c r="I2170" s="0" t="inlineStr">
         <is>
           <t>MVD p.9</t>
         </is>
       </c>
     </row>
     <row r="2171">
-      <c r="A2171" t="inlineStr">
+      <c r="A2171" s="0" t="inlineStr">
         <is>
           <t>पालन</t>
         </is>
       </c>
-      <c r="B2171" t="inlineStr">
+      <c r="B2171" s="0" t="inlineStr">
         <is>
           <t>adherence / observance</t>
         </is>
       </c>
-      <c r="C2171" t="inlineStr">
+      <c r="C2171" s="0" t="inlineStr">
         <is>
           <t>palan</t>
         </is>
       </c>
-      <c r="F2171" t="inlineStr">
+      <c r="F2171" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: समर्थन व पालन = endorsing and adhering.</t>
         </is>
       </c>
-      <c r="I2171" t="inlineStr">
+      <c r="I2171" s="0" t="inlineStr">
         <is>
           <t>MVD p.257</t>
         </is>
       </c>
     </row>
     <row r="2172">
-      <c r="A2172" t="inlineStr">
+      <c r="A2172" s="0" t="inlineStr">
         <is>
           <t>आधारित</t>
         </is>
       </c>
-      <c r="B2172" t="inlineStr">
+      <c r="B2172" s="0" t="inlineStr">
         <is>
           <t>based on</t>
         </is>
       </c>
-      <c r="C2172" t="inlineStr">
+      <c r="C2172" s="0" t="inlineStr">
         <is>
           <t>adharit</t>
         </is>
       </c>
-      <c r="F2172" t="inlineStr">
+      <c r="F2172" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: श्रम मूल्य… आधारित = based on evaluation and exchange of labour.</t>
         </is>
       </c>
-      <c r="I2172" t="inlineStr">
+      <c r="I2172" s="0" t="inlineStr">
         <is>
           <t>MVD p.269</t>
         </is>
       </c>
     </row>
     <row r="2173">
-      <c r="A2173" t="inlineStr">
+      <c r="A2173" s="0" t="inlineStr">
         <is>
           <t>समुदाय, समुदायों</t>
         </is>
       </c>
-      <c r="B2173" t="inlineStr">
+      <c r="B2173" s="0" t="inlineStr">
         <is>
           <t>community / communities</t>
         </is>
       </c>
-      <c r="C2173" t="inlineStr">
+      <c r="C2173" s="0" t="inlineStr">
         <is>
           <t>samuday</t>
         </is>
       </c>
-      <c r="F2173" t="inlineStr">
+      <c r="F2173" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: human communities formed around freedom from fear.</t>
         </is>
       </c>
-      <c r="I2173" t="inlineStr">
+      <c r="I2173" s="0" t="inlineStr">
         <is>
           <t>MVD p.20</t>
         </is>
       </c>
     </row>
     <row r="2174">
-      <c r="A2174" t="inlineStr">
+      <c r="A2174" s="0" t="inlineStr">
         <is>
           <t>अमानवीय दृष्टि</t>
         </is>
       </c>
-      <c r="B2174" t="inlineStr">
+      <c r="B2174" s="0" t="inlineStr">
         <is>
           <t>inhumane perspective</t>
         </is>
       </c>
-      <c r="C2174" t="inlineStr">
+      <c r="C2174" s="0" t="inlineStr">
         <is>
           <t>amanviya drishti</t>
         </is>
       </c>
-      <c r="F2174" t="inlineStr">
+      <c r="F2174" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: explicit MVD gloss Inhumane Perspective (amanveeya drishti).</t>
         </is>
       </c>
-      <c r="I2174" t="inlineStr">
+      <c r="I2174" s="0" t="inlineStr">
         <is>
           <t>MVD p.58</t>
         </is>
       </c>
     </row>
     <row r="2175">
-      <c r="A2175" t="inlineStr">
+      <c r="A2175" s="0" t="inlineStr">
         <is>
           <t>असंतुलन</t>
         </is>
       </c>
-      <c r="B2175" t="inlineStr">
+      <c r="B2175" s="0" t="inlineStr">
         <is>
           <t>imbalance / disparity</t>
         </is>
       </c>
-      <c r="C2175" t="inlineStr">
+      <c r="C2175" s="0" t="inlineStr">
         <is>
           <t>asantulan</t>
         </is>
       </c>
-      <c r="F2175" t="inlineStr">
+      <c r="F2175" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अमीरी-गरीबी का असंतुलन = disparity between rich and poor.</t>
         </is>
       </c>
-      <c r="I2175" t="inlineStr">
+      <c r="I2175" s="0" t="inlineStr">
         <is>
           <t>MVD p.267</t>
         </is>
       </c>
     </row>
     <row r="2176">
-      <c r="A2176" t="inlineStr">
+      <c r="A2176" s="0" t="inlineStr">
         <is>
           <t>आर्थिक सुरक्षा</t>
         </is>
       </c>
-      <c r="B2176" t="inlineStr">
+      <c r="B2176" s="0" t="inlineStr">
         <is>
           <t>economic security</t>
         </is>
       </c>
-      <c r="C2176" t="inlineStr">
+      <c r="C2176" s="0" t="inlineStr">
         <is>
           <t>arthik suraksha</t>
         </is>
       </c>
-      <c r="F2176" t="inlineStr">
+      <c r="F2176" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: explicit MVD heading Economic Security.</t>
         </is>
       </c>
-      <c r="I2176" t="inlineStr">
+      <c r="I2176" s="0" t="inlineStr">
         <is>
           <t>MVD p.265</t>
         </is>
       </c>
     </row>
     <row r="2177">
-      <c r="A2177" t="inlineStr">
+      <c r="A2177" s="0" t="inlineStr">
         <is>
           <t>इकाईयाँ</t>
         </is>
       </c>
-      <c r="B2177" t="inlineStr">
+      <c r="B2177" s="0" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="C2177" t="inlineStr">
+      <c r="C2177" s="0" t="inlineStr">
         <is>
           <t>ikaiyan</t>
         </is>
       </c>
-      <c r="F2177" t="inlineStr">
+      <c r="F2177" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: इकाईयाँ अनंत = units are countless.</t>
         </is>
       </c>
-      <c r="I2177" t="inlineStr">
+      <c r="I2177" s="0" t="inlineStr">
         <is>
           <t>MVD p.34</t>
         </is>
       </c>
     </row>
     <row r="2178">
-      <c r="A2178" t="inlineStr">
+      <c r="A2178" s="0" t="inlineStr">
         <is>
           <t>नियंत्रित, नियन्त्रण</t>
         </is>
       </c>
-      <c r="B2178" t="inlineStr">
+      <c r="B2178" s="0" t="inlineStr">
         <is>
           <t>regulated / regulation</t>
         </is>
       </c>
-      <c r="C2178" t="inlineStr">
+      <c r="C2178" s="0" t="inlineStr">
         <is>
           <t>niyantrit</t>
         </is>
       </c>
-      <c r="F2178" t="inlineStr">
+      <c r="F2178" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: प्रकृति नियंत्रित एवं संरक्षित = nature regulated and conserved; नियन्त्रण = regulation of prana.</t>
         </is>
       </c>
-      <c r="I2178" t="inlineStr">
+      <c r="I2178" s="0" t="inlineStr">
         <is>
           <t>MVD p.26</t>
         </is>
       </c>
     </row>
     <row r="2179">
-      <c r="A2179" t="inlineStr">
+      <c r="A2179" s="0" t="inlineStr">
         <is>
           <t>पृथ्वी</t>
         </is>
       </c>
-      <c r="B2179" t="inlineStr">
+      <c r="B2179" s="0" t="inlineStr">
         <is>
           <t>Earth</t>
         </is>
       </c>
-      <c r="C2179" t="inlineStr">
+      <c r="C2179" s="0" t="inlineStr">
         <is>
           <t>prithvi</t>
         </is>
       </c>
-      <c r="F2179" t="inlineStr">
+      <c r="F2179" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: Geography is study of the Earth's structure.</t>
         </is>
       </c>
-      <c r="I2179" t="inlineStr">
+      <c r="I2179" s="0" t="inlineStr">
         <is>
           <t>MVD p.136</t>
         </is>
       </c>
     </row>
     <row r="2180">
-      <c r="A2180" t="inlineStr">
+      <c r="A2180" s="0" t="inlineStr">
         <is>
           <t>शाकाहारी</t>
         </is>
       </c>
-      <c r="B2180" t="inlineStr">
+      <c r="B2180" s="0" t="inlineStr">
         <is>
           <t>herbivorous</t>
         </is>
       </c>
-      <c r="C2180" t="inlineStr">
+      <c r="C2180" s="0" t="inlineStr">
         <is>
           <t>shakahari</t>
         </is>
       </c>
-      <c r="F2180" t="inlineStr">
+      <c r="F2180" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: शाकाहारी और मांसाहारी = herbivorous and carnivorous.</t>
         </is>
       </c>
-      <c r="I2180" t="inlineStr">
+      <c r="I2180" s="0" t="inlineStr">
         <is>
           <t>SB p.17</t>
         </is>
       </c>
     </row>
     <row r="2181">
-      <c r="A2181" t="inlineStr">
+      <c r="A2181" s="0" t="inlineStr">
         <is>
           <t>मांसाहारी</t>
         </is>
       </c>
-      <c r="B2181" t="inlineStr">
+      <c r="B2181" s="0" t="inlineStr">
         <is>
           <t>carnivorous</t>
         </is>
       </c>
-      <c r="C2181" t="inlineStr">
+      <c r="C2181" s="0" t="inlineStr">
         <is>
           <t>mansahari</t>
         </is>
       </c>
-      <c r="F2181" t="inlineStr">
+      <c r="F2181" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: paired with शाकाहारी in SB animal-order discussion.</t>
         </is>
       </c>
-      <c r="I2181" t="inlineStr">
+      <c r="I2181" s="0" t="inlineStr">
         <is>
           <t>SB p.17</t>
         </is>
       </c>
     </row>
     <row r="2182">
-      <c r="A2182" t="inlineStr">
+      <c r="A2182" s="0" t="inlineStr">
         <is>
           <t>सम्पर्क</t>
         </is>
       </c>
-      <c r="B2182" t="inlineStr">
+      <c r="B2182" s="0" t="inlineStr">
         <is>
           <t>association / contact</t>
         </is>
       </c>
-      <c r="C2182" t="inlineStr">
+      <c r="C2182" s="0" t="inlineStr">
         <is>
           <t>sampark</t>
         </is>
       </c>
-      <c r="F2182" t="inlineStr">
+      <c r="F2182" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: सम्पर्क एवं संबंध = associations and relationships (paired with संबंध).</t>
         </is>
       </c>
-      <c r="I2182" t="inlineStr">
+      <c r="I2182" s="0" t="inlineStr">
         <is>
           <t>MVD p.242</t>
         </is>
       </c>
     </row>
     <row r="2183">
-      <c r="A2183" t="inlineStr">
+      <c r="A2183" s="0" t="inlineStr">
         <is>
           <t>स्वर्ग</t>
         </is>
       </c>
-      <c r="B2183" t="inlineStr">
+      <c r="B2183" s="0" t="inlineStr">
         <is>
           <t>heaven / heavenly</t>
         </is>
       </c>
-      <c r="C2183" t="inlineStr">
+      <c r="C2183" s="0" t="inlineStr">
         <is>
           <t>svarg</t>
         </is>
       </c>
-      <c r="F2183" t="inlineStr">
+      <c r="F2183" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: भूमि स्वर्ग हो = May the Earth be heavenly.</t>
         </is>
       </c>
-      <c r="I2183" t="inlineStr">
+      <c r="I2183" s="0" t="inlineStr">
         <is>
           <t>MVD p.9</t>
         </is>
       </c>
     </row>
     <row r="2184">
-      <c r="A2184" t="inlineStr">
+      <c r="A2184" s="0" t="inlineStr">
         <is>
           <t>अधिकतम</t>
         </is>
       </c>
-      <c r="B2184" t="inlineStr">
+      <c r="B2184" s="0" t="inlineStr">
         <is>
           <t>maximum</t>
         </is>
       </c>
-      <c r="C2184" t="inlineStr">
+      <c r="C2184" s="0" t="inlineStr">
         <is>
           <t>adhiktam</t>
         </is>
       </c>
-      <c r="F2184" t="inlineStr">
+      <c r="F2184" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: अधिकतम श्रम = maximum effort.</t>
         </is>
       </c>
-      <c r="I2184" t="inlineStr">
+      <c r="I2184" s="0" t="inlineStr">
         <is>
           <t>MVD p.266</t>
         </is>
       </c>
     </row>
     <row r="2185">
-      <c r="A2185" t="inlineStr">
+      <c r="A2185" s="0" t="inlineStr">
         <is>
           <t>निरन्तरता</t>
         </is>
       </c>
-      <c r="B2185" t="inlineStr">
+      <c r="B2185" s="0" t="inlineStr">
         <is>
           <t>continuity</t>
         </is>
       </c>
-      <c r="C2185" t="inlineStr">
+      <c r="C2185" s="0" t="inlineStr">
         <is>
           <t>nirantarta</t>
         </is>
       </c>
-      <c r="F2185" t="inlineStr">
+      <c r="F2185" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: कृतज्ञता की निरन्तरता = continuity of gratitude.</t>
         </is>
       </c>
-      <c r="I2185" t="inlineStr">
+      <c r="I2185" s="0" t="inlineStr">
         <is>
           <t>MVD p.29</t>
         </is>
       </c>
     </row>
     <row r="2186">
-      <c r="A2186" t="inlineStr">
+      <c r="A2186" s="0" t="inlineStr">
         <is>
           <t>स्व पुरुष</t>
         </is>
       </c>
-      <c r="B2186" t="inlineStr">
+      <c r="B2186" s="0" t="inlineStr">
         <is>
           <t>one's husband / marital faithfulness (contextual)</t>
         </is>
       </c>
-      <c r="C2186" t="inlineStr">
+      <c r="C2186" s="0" t="inlineStr">
         <is>
           <t>sva purush</t>
         </is>
       </c>
-      <c r="F2186" t="inlineStr">
+      <c r="F2186" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: स्वनारी/स्व पुरुष in the righteous-wealth / marital-faithfulness policy triad.</t>
         </is>
       </c>
-      <c r="I2186" t="inlineStr">
+      <c r="I2186" s="0" t="inlineStr">
         <is>
           <t>MVD p.267</t>
         </is>
       </c>
     </row>
     <row r="2187">
-      <c r="A2187" t="inlineStr">
+      <c r="A2187" s="0" t="inlineStr">
         <is>
           <t>प्रवृत्ति, प्रवृत्तियाँ</t>
         </is>
       </c>
-      <c r="B2187" t="inlineStr">
+      <c r="B2187" s="0" t="inlineStr">
         <is>
           <t>tendency / tendencies</t>
         </is>
       </c>
-      <c r="C2187" t="inlineStr">
+      <c r="C2187" s="0" t="inlineStr">
         <is>
           <t>pravritti</t>
         </is>
       </c>
-      <c r="F2187" t="inlineStr">
+      <c r="F2187" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: विचार व प्रवृत्तियाँ = thoughts and tendencies.</t>
         </is>
       </c>
-      <c r="I2187" t="inlineStr">
+      <c r="I2187" s="0" t="inlineStr">
         <is>
           <t>MVD p.211</t>
         </is>
       </c>
     </row>
     <row r="2188">
-      <c r="A2188" t="inlineStr">
+      <c r="A2188" s="0" t="inlineStr">
         <is>
           <t>प्रसन्नता</t>
         </is>
       </c>
-      <c r="B2188" t="inlineStr">
+      <c r="B2188" s="0" t="inlineStr">
         <is>
           <t>happiness / gladly</t>
         </is>
       </c>
-      <c r="C2188" t="inlineStr">
+      <c r="C2188" s="0" t="inlineStr">
         <is>
           <t>prasannata</t>
         </is>
       </c>
-      <c r="F2188" t="inlineStr">
+      <c r="F2188" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: प्रसन्नता पूर्वक = happily (generosity definition).</t>
         </is>
       </c>
-      <c r="I2188" t="inlineStr">
+      <c r="I2188" s="0" t="inlineStr">
         <is>
           <t>MVD p.52</t>
         </is>
       </c>
     </row>
     <row r="2189">
-      <c r="A2189" t="inlineStr">
+      <c r="A2189" s="0" t="inlineStr">
         <is>
           <t>मनुष्य</t>
         </is>
       </c>
-      <c r="B2189" t="inlineStr">
+      <c r="B2189" s="0" t="inlineStr">
         <is>
           <t>human / humans</t>
         </is>
       </c>
-      <c r="C2189" t="inlineStr">
+      <c r="C2189" s="0" t="inlineStr">
         <is>
           <t>manushya</t>
         </is>
       </c>
-      <c r="F2189" t="inlineStr">
+      <c r="F2189" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: मनुष्य देवता हो = May humans be deities.</t>
         </is>
       </c>
-      <c r="I2189" t="inlineStr">
+      <c r="I2189" s="0" t="inlineStr">
         <is>
           <t>MVD p.9</t>
         </is>
       </c>
     </row>
     <row r="2190">
-      <c r="A2190" t="inlineStr">
+      <c r="A2190" s="0" t="inlineStr">
         <is>
           <t>वर्ग विहीन</t>
         </is>
       </c>
-      <c r="B2190" t="inlineStr">
+      <c r="B2190" s="0" t="inlineStr">
         <is>
           <t>classless</t>
         </is>
       </c>
-      <c r="C2190" t="inlineStr">
+      <c r="C2190" s="0" t="inlineStr">
         <is>
           <t>varg vihin</t>
         </is>
       </c>
-      <c r="F2190" t="inlineStr">
+      <c r="F2190" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: वर्ग विहीन समाज = classless society.</t>
         </is>
       </c>
-      <c r="I2190" t="inlineStr">
+      <c r="I2190" s="0" t="inlineStr">
         <is>
           <t>MVD p.21</t>
         </is>
       </c>
     </row>
     <row r="2191">
-      <c r="A2191" t="inlineStr">
+      <c r="A2191" s="0" t="inlineStr">
         <is>
           <t>वैयक्तिक</t>
         </is>
       </c>
-      <c r="B2191" t="inlineStr">
+      <c r="B2191" s="0" t="inlineStr">
         <is>
           <t>individual</t>
         </is>
       </c>
-      <c r="C2191" t="inlineStr">
+      <c r="C2191" s="0" t="inlineStr">
         <is>
           <t>vaiyaktik</t>
         </is>
       </c>
-      <c r="F2191" t="inlineStr">
+      <c r="F2191" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: वैयक्तिक जीवन व जीविका = individual life and livelihood.</t>
         </is>
       </c>
-      <c r="I2191" t="inlineStr">
+      <c r="I2191" s="0" t="inlineStr">
         <is>
           <t>MVD p.168</t>
         </is>
       </c>
     </row>
     <row r="2192">
-      <c r="A2192" t="inlineStr">
+      <c r="A2192" s="0" t="inlineStr">
         <is>
           <t>संरक्षित</t>
         </is>
       </c>
-      <c r="B2192" t="inlineStr">
+      <c r="B2192" s="0" t="inlineStr">
         <is>
           <t>protected / conserved</t>
         </is>
       </c>
-      <c r="C2192" t="inlineStr">
+      <c r="C2192" s="0" t="inlineStr">
         <is>
           <t>sanrakshit</t>
         </is>
       </c>
-      <c r="F2192" t="inlineStr">
+      <c r="F2192" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: नियंत्रित तथा संरक्षित = regulated and protected/conserved.</t>
         </is>
       </c>
-      <c r="I2192" t="inlineStr">
+      <c r="I2192" s="0" t="inlineStr">
         <is>
           <t>MVD p.144</t>
         </is>
       </c>
     </row>
     <row r="2193">
-      <c r="A2193" t="inlineStr">
+      <c r="A2193" s="0" t="inlineStr">
         <is>
           <t>योग्य</t>
         </is>
       </c>
-      <c r="B2193" t="inlineStr">
+      <c r="B2193" s="0" t="inlineStr">
         <is>
           <t>fit / worthy / suitable</t>
         </is>
       </c>
-      <c r="C2193" t="inlineStr">
+      <c r="C2193" s="0" t="inlineStr">
         <is>
           <t>yogya</t>
         </is>
       </c>
-      <c r="F2193" t="inlineStr">
+      <c r="F2193" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: योगानुभूति योग्य विकास = development fit for realisation of yog; distinct from योग्यता (ability).</t>
         </is>
       </c>
-      <c r="I2193" t="inlineStr">
+      <c r="I2193" s="0" t="inlineStr">
         <is>
           <t>MVD p.165</t>
         </is>
       </c>
     </row>
     <row r="2194">
-      <c r="A2194" t="inlineStr">
+      <c r="A2194" s="0" t="inlineStr">
         <is>
           <t>सुलभ</t>
         </is>
       </c>
-      <c r="B2194" t="inlineStr">
+      <c r="B2194" s="0" t="inlineStr">
         <is>
           <t>accessible</t>
         </is>
       </c>
-      <c r="C2194" t="inlineStr">
+      <c r="C2194" s="0" t="inlineStr">
         <is>
           <t>sulabh</t>
         </is>
       </c>
-      <c r="F2194" t="inlineStr">
+      <c r="F2194" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: समाधान व समझ सुलभ = resolution and understanding become accessible.</t>
         </is>
       </c>
-      <c r="I2194" t="inlineStr">
+      <c r="I2194" s="0" t="inlineStr">
         <is>
           <t>MVD p.290</t>
         </is>
       </c>
     </row>
     <row r="2195">
-      <c r="A2195" t="inlineStr">
+      <c r="A2195" s="0" t="inlineStr">
         <is>
           <t>संभव</t>
         </is>
       </c>
-      <c r="B2195" t="inlineStr">
+      <c r="B2195" s="0" t="inlineStr">
         <is>
           <t>possible</t>
         </is>
       </c>
-      <c r="C2195" t="inlineStr">
+      <c r="C2195" s="0" t="inlineStr">
         <is>
           <t>sambhav</t>
         </is>
       </c>
-      <c r="F2195" t="inlineStr">
+      <c r="F2195" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: …से ही संभव है = is possible only through…</t>
         </is>
       </c>
-      <c r="I2195" t="inlineStr">
+      <c r="I2195" s="0" t="inlineStr">
         <is>
           <t>MVD p.172</t>
         </is>
       </c>
     </row>
     <row r="2196">
-      <c r="A2196" t="inlineStr">
+      <c r="A2196" s="0" t="inlineStr">
         <is>
           <t>स्थान</t>
         </is>
       </c>
-      <c r="B2196" t="inlineStr">
+      <c r="B2196" s="0" t="inlineStr">
         <is>
           <t>place / position</t>
         </is>
       </c>
-      <c r="C2196" t="inlineStr">
+      <c r="C2196" s="0" t="inlineStr">
         <is>
           <t>sthan</t>
         </is>
       </c>
-      <c r="F2196" t="inlineStr">
+      <c r="F2196" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: महत्वपूर्ण स्थान = significant position/place.</t>
         </is>
       </c>
-      <c r="I2196" t="inlineStr">
+      <c r="I2196" s="0" t="inlineStr">
         <is>
           <t>MVD p.192</t>
         </is>
       </c>
     </row>
     <row r="2197">
-      <c r="A2197" t="inlineStr">
+      <c r="A2197" s="0" t="inlineStr">
         <is>
           <t>स्वरुप, स्वरूप</t>
         </is>
       </c>
-      <c r="B2197" t="inlineStr">
+      <c r="B2197" s="0" t="inlineStr">
         <is>
           <t>form / aspect</t>
         </is>
       </c>
-      <c r="C2197" t="inlineStr">
+      <c r="C2197" s="0" t="inlineStr">
         <is>
           <t>svarup</t>
         </is>
       </c>
-      <c r="F2197" t="inlineStr">
+      <c r="F2197" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: तीन स्वरुप में = under three headings/forms (theism categories).</t>
         </is>
       </c>
-      <c r="I2197" t="inlineStr">
+      <c r="I2197" s="0" t="inlineStr">
         <is>
           <t>SB p.24</t>
         </is>
       </c>
     </row>
     <row r="2198">
-      <c r="A2198" t="inlineStr">
+      <c r="A2198" s="0" t="inlineStr">
         <is>
           <t>नारी</t>
         </is>
       </c>
-      <c r="B2198" t="inlineStr">
+      <c r="B2198" s="0" t="inlineStr">
         <is>
           <t>woman / wife (contextual)</t>
         </is>
       </c>
-      <c r="C2198" t="inlineStr">
+      <c r="C2198" s="0" t="inlineStr">
         <is>
           <t>nari</t>
         </is>
       </c>
-      <c r="F2198" t="inlineStr">
+      <c r="F2198" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: स्व-नारी/पर-नारी in marital faithfulness vs adultery discussion.</t>
         </is>
       </c>
-      <c r="I2198" t="inlineStr">
+      <c r="I2198" s="0" t="inlineStr">
         <is>
           <t>MVD p.189</t>
         </is>
       </c>
     </row>
     <row r="2199">
-      <c r="A2199" t="inlineStr">
+      <c r="A2199" s="0" t="inlineStr">
         <is>
           <t>इंगित</t>
         </is>
       </c>
-      <c r="B2199" t="inlineStr">
+      <c r="B2199" s="0" t="inlineStr">
         <is>
           <t>indicated / signalled</t>
         </is>
       </c>
-      <c r="C2199" t="inlineStr">
+      <c r="C2199" s="0" t="inlineStr">
         <is>
           <t>ingit</t>
         </is>
       </c>
-      <c r="F2199" t="inlineStr">
+      <c r="F2199" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: इंगित होने वाले सम्पूर्ण संकेतों = all the signals indicated/received.</t>
         </is>
       </c>
-      <c r="I2199" t="inlineStr">
+      <c r="I2199" s="0" t="inlineStr">
         <is>
           <t>MVD p.345</t>
         </is>
       </c>
     </row>
     <row r="2200">
-      <c r="A2200" t="inlineStr">
+      <c r="A2200" s="0" t="inlineStr">
         <is>
           <t>उपलब्ध</t>
         </is>
       </c>
-      <c r="B2200" t="inlineStr">
+      <c r="B2200" s="0" t="inlineStr">
         <is>
           <t>available / allocated</t>
         </is>
       </c>
-      <c r="C2200" t="inlineStr">
+      <c r="C2200" s="0" t="inlineStr">
         <is>
           <t>upalabdh</t>
         </is>
       </c>
-      <c r="F2200" t="inlineStr">
+      <c r="F2200" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: साधन उपलब्ध कराना = allocating/making resources available.</t>
         </is>
       </c>
-      <c r="I2200" t="inlineStr">
+      <c r="I2200" s="0" t="inlineStr">
         <is>
           <t>MVD p.268</t>
         </is>
       </c>
     </row>
     <row r="2201">
-      <c r="A2201" t="inlineStr">
+      <c r="A2201" s="0" t="inlineStr">
         <is>
           <t>वृत्ति, वृति</t>
         </is>
       </c>
-      <c r="B2201" t="inlineStr">
+      <c r="B2201" s="0" t="inlineStr">
         <is>
           <t>vritti</t>
         </is>
       </c>
-      <c r="C2201" t="inlineStr">
+      <c r="C2201" s="0" t="inlineStr">
         <is>
           <t>vritti</t>
         </is>
       </c>
-      <c r="F2201" t="inlineStr">
+      <c r="F2201" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: kept as vritti in MVD English (mun → vritti → chitta → buddhi hierarchy).</t>
         </is>
       </c>
-      <c r="I2201" t="inlineStr">
+      <c r="I2201" s="0" t="inlineStr">
         <is>
           <t>MVD p.286</t>
         </is>
       </c>
     </row>
     <row r="2202">
-      <c r="A2202" t="inlineStr">
+      <c r="A2202" s="0" t="inlineStr">
         <is>
           <t>संदर्भ</t>
         </is>
       </c>
-      <c r="B2202" t="inlineStr">
+      <c r="B2202" s="0" t="inlineStr">
         <is>
           <t>context / respect (with respect to)</t>
         </is>
       </c>
-      <c r="C2202" t="inlineStr">
+      <c r="C2202" s="0" t="inlineStr">
         <is>
           <t>sandarbh</t>
         </is>
       </c>
-      <c r="F2202" t="inlineStr">
+      <c r="F2202" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: मानव के संदर्भ में = with respect to humans.</t>
         </is>
       </c>
-      <c r="I2202" t="inlineStr">
+      <c r="I2202" s="0" t="inlineStr">
         <is>
           <t>MVD p.231</t>
         </is>
       </c>
     </row>
     <row r="2203">
-      <c r="A2203" t="inlineStr">
+      <c r="A2203" s="0" t="inlineStr">
         <is>
           <t>क्षतिग्रस्त</t>
         </is>
       </c>
-      <c r="B2203" t="inlineStr">
+      <c r="B2203" s="0" t="inlineStr">
         <is>
           <t>damaged / destroyed</t>
         </is>
       </c>
-      <c r="C2203" t="inlineStr">
+      <c r="C2203" s="0" t="inlineStr">
         <is>
           <t>kshatigrast</t>
         </is>
       </c>
-      <c r="F2203" t="inlineStr">
+      <c r="F2203" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: सर्वाधिक क्षतिग्रस्त = maximum destruction/damage to nature.</t>
         </is>
       </c>
-      <c r="I2203" t="inlineStr">
+      <c r="I2203" s="0" t="inlineStr">
         <is>
           <t>SB p.18</t>
         </is>
       </c>
     </row>
     <row r="2204">
-      <c r="A2204" t="inlineStr">
+      <c r="A2204" s="0" t="inlineStr">
         <is>
           <t>रहस्यमय</t>
         </is>
       </c>
-      <c r="B2204" t="inlineStr">
+      <c r="B2204" s="0" t="inlineStr">
         <is>
           <t>mysterious</t>
         </is>
       </c>
-      <c r="C2204" t="inlineStr">
+      <c r="C2204" s="0" t="inlineStr">
         <is>
           <t>rahasyamay</t>
         </is>
       </c>
-      <c r="F2204" t="inlineStr">
+      <c r="F2204" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: रहस्यमय लगता है = may seem mysterious.</t>
         </is>
       </c>
-      <c r="I2204" t="inlineStr">
+      <c r="I2204" s="0" t="inlineStr">
         <is>
           <t>MVD p.295</t>
         </is>
       </c>
     </row>
     <row r="2205">
-      <c r="A2205" t="inlineStr">
+      <c r="A2205" s="0" t="inlineStr">
         <is>
           <t>समाहित</t>
         </is>
       </c>
-      <c r="B2205" t="inlineStr">
+      <c r="B2205" s="0" t="inlineStr">
         <is>
           <t>encompassed / included</t>
         </is>
       </c>
-      <c r="C2205" t="inlineStr">
+      <c r="C2205" s="0" t="inlineStr">
         <is>
           <t>samahit</t>
         </is>
       </c>
-      <c r="F2205" t="inlineStr">
+      <c r="F2205" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: व्यापक में समाहित = encompassed within omnipresence.</t>
         </is>
       </c>
-      <c r="I2205" t="inlineStr">
+      <c r="I2205" s="0" t="inlineStr">
         <is>
           <t>MVD p.97</t>
         </is>
       </c>
     </row>
     <row r="2206">
-      <c r="A2206" t="inlineStr">
+      <c r="A2206" s="0" t="inlineStr">
         <is>
           <t>स्वाभाविक</t>
         </is>
       </c>
-      <c r="B2206" t="inlineStr">
+      <c r="B2206" s="0" t="inlineStr">
         <is>
           <t>natural / typically</t>
         </is>
       </c>
-      <c r="C2206" t="inlineStr">
+      <c r="C2206" s="0" t="inlineStr">
         <is>
           <t>svabhavik</t>
         </is>
       </c>
-      <c r="F2206" t="inlineStr">
+      <c r="F2206" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: typically/naturally occurs (brother-sister recognition).</t>
         </is>
       </c>
-      <c r="I2206" t="inlineStr">
+      <c r="I2206" s="0" t="inlineStr">
         <is>
           <t>MVD p.250</t>
         </is>
       </c>
     </row>
     <row r="2207">
-      <c r="A2207" t="inlineStr">
+      <c r="A2207" s="0" t="inlineStr">
         <is>
           <t>धातु युग</t>
         </is>
       </c>
-      <c r="B2207" t="inlineStr">
+      <c r="B2207" s="0" t="inlineStr">
         <is>
           <t>Iron Age</t>
         </is>
       </c>
-      <c r="C2207" t="inlineStr">
+      <c r="C2207" s="0" t="inlineStr">
         <is>
           <t>dhatu yug</t>
         </is>
       </c>
-      <c r="F2207" t="inlineStr">
+      <c r="F2207" s="0" t="inlineStr">
         <is>
           <t>Phase 4 curated: SB periodization Stone Age to Iron Age (धातु युग).</t>
         </is>
       </c>
-      <c r="I2207" t="inlineStr">
+      <c r="I2207" s="0" t="inlineStr">
         <is>
           <t>SB p.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>मध्यांश</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>nucleus</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>madhyansh</t>
+        </is>
+      </c>
+      <c r="F2208" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.1/3.11 — central particle(s) of the atom. Settled per Raghava.</t>
+        </is>
+      </c>
+      <c r="I2208" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.1/3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>अच्छी दूरी</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>good distance</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>acchi doori</t>
+        </is>
+      </c>
+      <c r="F2209" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): equilibrium separation maintained by the nucleus / between bodies.</t>
+        </is>
+      </c>
+      <c r="I2209" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>मध्यस्थीयकरण</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>mediation</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>madhyasthiyakaran</t>
+        </is>
+      </c>
+      <c r="F2210" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.11 — what modern force/power studies are said to deny.</t>
+        </is>
+      </c>
+      <c r="I2210" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>चुम्बकीय धारा</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>magnetic current</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>chumbakiya dhara</t>
+        </is>
+      </c>
+      <c r="F2211" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.13 — electricity as flow from its fragmentation.</t>
+        </is>
+      </c>
+      <c r="I2211" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>विद्युतवाहिता</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>electric conduction</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>vidyutvahita</t>
+        </is>
+      </c>
+      <c r="F2212" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.13 — radio/TV waves as electricity-borne word/sound.</t>
+        </is>
+      </c>
+      <c r="I2212" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>संकोचन प्रसारण</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>contraction-expansion</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>sankochan prasaran</t>
+        </is>
+      </c>
+      <c r="F2213" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.13 — mechanism of flow/pressure in a medium.</t>
+        </is>
+      </c>
+      <c r="I2213" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>अण्डाकार</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>elliptic</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>andakar</t>
+        </is>
+      </c>
+      <c r="F2214" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7 — Earth's orbital path. Settled per Raghava.</t>
+        </is>
+      </c>
+      <c r="I2214" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>ससम्मुखता</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>facing-ness</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>sasammukhta</t>
+        </is>
+      </c>
+      <c r="F2215" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7 — Earth's face toward the Sun.</t>
+        </is>
+      </c>
+      <c r="I2215" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>सौर व्यूह</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>solar system (solar array)</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>saur vyuh</t>
+        </is>
+      </c>
+      <c r="F2216" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7/3.11.</t>
+        </is>
+      </c>
+      <c r="I2216" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7/3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>ग्रह-गोल</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>planet-orb</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>grah-gol</t>
+        </is>
+      </c>
+      <c r="F2217" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7.</t>
+        </is>
+      </c>
+      <c r="I2217" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>संक्रमणीयता</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>transition-ness</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>sankramaniyata</t>
+        </is>
+      </c>
+      <c r="F2218" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.3 abstract noun of संक्रमण (transition).</t>
+        </is>
+      </c>
+      <c r="I2218" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>विकिरणीयता</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>radiativeness</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>vikiraniyata</t>
+        </is>
+      </c>
+      <c r="F2219" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.3 — emission property of undigested atoms.</t>
+        </is>
+      </c>
+      <c r="I2219" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>विकिरणीय द्रव्य</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>radiant (radioactive) materials</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>vikiraniya dravya</t>
+        </is>
+      </c>
+      <c r="F2220" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.11.</t>
+        </is>
+      </c>
+      <c r="I2220" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>संतुलनीकरण</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>equilibration</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>santulanikaran</t>
+        </is>
+      </c>
+      <c r="F2221" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7.</t>
+        </is>
+      </c>
+      <c r="I2221" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>आवर्तनशीलता</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>cyclicality</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>avartansheelta</t>
+        </is>
+      </c>
+      <c r="F2222" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7/3.15 — water cycle; recurrence basis of time-reckoning.</t>
+        </is>
+      </c>
+      <c r="I2222" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7/3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>तापोद्दीपन</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>heat-stimulation</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>tapoddipan</t>
+        </is>
+      </c>
+      <c r="F2223" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.7.</t>
+        </is>
+      </c>
+      <c r="I2223" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>समकेन्द्रीय रेखा</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>concentric line</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>samkendriya rekha</t>
+        </is>
+      </c>
+      <c r="F2224" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.14.</t>
+        </is>
+      </c>
+      <c r="I2224" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>घटी, पल</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>ghati, pal (time units)</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>ghati, pal</t>
+        </is>
+      </c>
+      <c r="F2225" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.15 — left transliterated as traditional time units.</t>
+        </is>
+      </c>
+      <c r="I2225" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>चिराकांक्षा, चिराकाँक्षा</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>abiding aspiration</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>chira-akanksha</t>
+        </is>
+      </c>
+      <c r="F2226" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.6 — चिर (lasting) + आकांक्षा (aspiration).</t>
+        </is>
+      </c>
+      <c r="I2226" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>सचेष्ट</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>earnestly active</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>sachesht</t>
+        </is>
+      </c>
+      <c r="F2227" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.6 — alert, diligent striving toward the human goal.</t>
+        </is>
+      </c>
+      <c r="I2227" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>ब्रह्मवाद, आत्मवाद, जातिवाद, नस्लवाद, वंशवाद</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>Brahma-doctrine, self-doctrine, casteism, racism, lineage-ism</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>brahmavad, atmavad, jativad, naslvad, vanshvad</t>
+        </is>
+      </c>
+      <c r="F2228" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.16 — compositional -वाद (doctrine/ism) compounds.</t>
+        </is>
+      </c>
+      <c r="I2228" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>उद्घाता</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>herald</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>udghata</t>
+        </is>
+      </c>
+      <c r="F2229" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.18 — human being as one who announces/evidences awakened status.</t>
+        </is>
+      </c>
+      <c r="I2229" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>औकात</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>standing</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>aukat</t>
+        </is>
+      </c>
+      <c r="F2230" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 3.16 — capacity/standing of human body-composition across generations.</t>
+        </is>
+      </c>
+      <c r="I2230" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>वेदना</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>vedana</t>
+        </is>
+      </c>
+      <c r="F2231" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — pressure of accepting the unacceptable; distinct from संवेदना (sensation).</t>
+        </is>
+      </c>
+      <c r="I2231" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1; MVD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>मति, सुमति, अनुमति</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>mati, sumati, anumati (left transliterated)</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>mati, sumati, anumati</t>
+        </is>
+      </c>
+      <c r="F2232" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — triad of righteous-action-born intellect (सुकर्म-जन्य-बुद्धि); left transliterated.</t>
+        </is>
+      </c>
+      <c r="I2232" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>अमति, कुमति, दुर्मति</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>amati, kumati, durmati (left transliterated)</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>amati, kumati, durmati</t>
+        </is>
+      </c>
+      <c r="F2233" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — triad of unrighteous-action-born tendency; parallel to मति/सुमति/अनुमति.</t>
+        </is>
+      </c>
+      <c r="I2233" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>पुण्यात्मा, पापात्मा</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>the meritorious soul, the sinful soul</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>punyatma, papatma</t>
+        </is>
+      </c>
+      <c r="F2234" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — compositional pair with सुखी/दुखी across five states.</t>
+        </is>
+      </c>
+      <c r="I2234" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>रजोगुण, तमोगुण, सत्वगुण</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>rajoguna, tamoguna, sattvaguna</t>
+        </is>
+      </c>
+      <c r="F2235" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — classical three गुण; mapped onto sam/visham/mediating.</t>
+        </is>
+      </c>
+      <c r="I2235" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>मानवीयतापूर्ण (X), अतिमानवीयतापूर्ण (X)</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>humane (X) / higher-humane (X)</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>manviyatapurna, atimanviyatapurna</t>
+        </is>
+      </c>
+      <c r="F2236" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): pattern rule — X-पूर्ण as plain adjective (humane / higher-humane), not "X-replete-with-humaneness". Distinct from bare मानवीयता nouns and other -पूर्ण compounds.</t>
+        </is>
+      </c>
+      <c r="I2236" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; MVD p.3, p.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>गम्यता</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>the destination</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>gamyata</t>
+        </is>
+      </c>
+      <c r="F2237" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 1 — abstract noun of गम्य/गन्तव्य (destination).</t>
+        </is>
+      </c>
+      <c r="I2237" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>सद्विवेक</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>right-wisdom</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>sad-vivek</t>
+        </is>
+      </c>
+      <c r="F2238" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 2 — सत् + विवेक; parallel to सम्यक्-बोध.</t>
+        </is>
+      </c>
+      <c r="I2238" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>सर्वमंगल, मांगल्य</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>universal welfare, welfare</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>sarva mangal, mangalya</t>
+        </is>
+      </c>
+      <c r="F2239" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 2 — shared aim of upasanas; मांगल्य abstract cognate.</t>
+        </is>
+      </c>
+      <c r="I2239" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>न्यूनातिरेक</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>deficiency-or-excess</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>nyoonatirek</t>
+        </is>
+      </c>
+      <c r="F2240" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 2 — न्यून + अतिरेक; faulty (imposed) self-evaluation.</t>
+        </is>
+      </c>
+      <c r="I2240" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>साम्राज्य</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>dominion</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>samrajya</t>
+        </is>
+      </c>
+      <c r="F2241" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 2 — "dominion" (not "sovereignty") to keep distinct from प्रभुसत्ता.</t>
+        </is>
+      </c>
+      <c r="I2241" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>पाण्डित्य</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>scholarliness</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>panditya</t>
+        </is>
+      </c>
+      <c r="F2242" t="inlineStr">
+        <is>
+          <t>KD glossary addition (2026-07): KD 2 — first KD appearance at p.31 (निपुणता एवं कुशलता, पाण्डित्य).</t>
+        </is>
+      </c>
+      <c r="I2242" t="inlineStr">
+        <is>
+          <t>KD-Glossary-Additions.md; KD 2</t>
         </is>
       </c>
     </row>
